--- a/stella/test_fixtures/inventory_risk/iri_data.xlsx
+++ b/stella/test_fixtures/inventory_risk/iri_data.xlsx
@@ -499,22 +499,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15491.46</v>
+        <v>15028.5</v>
       </c>
       <c r="E2" t="n">
-        <v>413.1</v>
+        <v>400.8</v>
       </c>
       <c r="F2" t="n">
         <v>6.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2551</v>
+        <v>0.2532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2544</v>
+        <v>0.2525</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15104.55</v>
+        <v>14522.01</v>
       </c>
       <c r="E3" t="n">
-        <v>402.8</v>
+        <v>387.3</v>
       </c>
       <c r="F3" t="n">
         <v>6.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2487</v>
+        <v>0.2447</v>
       </c>
       <c r="H3" t="n">
-        <v>0.248</v>
+        <v>0.2439</v>
       </c>
       <c r="I3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -571,22 +571,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16653.96</v>
+        <v>16632.16</v>
       </c>
       <c r="E4" t="n">
-        <v>462.6</v>
+        <v>462</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2742</v>
+        <v>0.2803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2849</v>
+        <v>0.291</v>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13475.93</v>
+        <v>13160.74</v>
       </c>
       <c r="E5" t="n">
-        <v>345.5</v>
+        <v>337.5</v>
       </c>
       <c r="F5" t="n">
         <v>6.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2219</v>
+        <v>0.2218</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2128</v>
+        <v>0.2126</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15500.81</v>
+        <v>15575.48</v>
       </c>
       <c r="E6" t="n">
-        <v>413.4</v>
+        <v>415.3</v>
       </c>
       <c r="F6" t="n">
         <v>6.25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2587</v>
+        <v>0.2541</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2581</v>
+        <v>0.2534</v>
       </c>
       <c r="I6" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15157</v>
+        <v>15362.43</v>
       </c>
       <c r="E7" t="n">
-        <v>404.2</v>
+        <v>409.7</v>
       </c>
       <c r="F7" t="n">
         <v>6.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.253</v>
+        <v>0.2506</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2524</v>
+        <v>0.2499</v>
       </c>
       <c r="I7" t="n">
         <v>88</v>
@@ -715,22 +715,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15782.05</v>
+        <v>16562.2</v>
       </c>
       <c r="E8" t="n">
-        <v>438.4</v>
+        <v>460.1</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2634</v>
+        <v>0.2702</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2738</v>
+        <v>0.2807</v>
       </c>
       <c r="I8" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -751,19 +751,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13474.03</v>
+        <v>13805.59</v>
       </c>
       <c r="E9" t="n">
-        <v>345.5</v>
+        <v>354</v>
       </c>
       <c r="F9" t="n">
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2249</v>
+        <v>0.2252</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2157</v>
+        <v>0.216</v>
       </c>
       <c r="I9" t="n">
         <v>90</v>
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14769.04</v>
+        <v>15429.09</v>
       </c>
       <c r="E10" t="n">
-        <v>393.8</v>
+        <v>411.4</v>
       </c>
       <c r="F10" t="n">
         <v>6.25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2509</v>
+        <v>0.2561</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2504</v>
+        <v>0.2556</v>
       </c>
       <c r="I10" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15118.17</v>
+        <v>14955.36</v>
       </c>
       <c r="E11" t="n">
-        <v>403.2</v>
+        <v>398.8</v>
       </c>
       <c r="F11" t="n">
         <v>6.25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2569</v>
+        <v>0.2483</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2563</v>
+        <v>0.2477</v>
       </c>
       <c r="I11" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15561.48</v>
+        <v>16051.08</v>
       </c>
       <c r="E12" t="n">
-        <v>432.3</v>
+        <v>445.9</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2644</v>
+        <v>0.2665</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2748</v>
+        <v>0.2769</v>
       </c>
       <c r="I12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -895,22 +895,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13407.6</v>
+        <v>13802.4</v>
       </c>
       <c r="E13" t="n">
-        <v>343.8</v>
+        <v>353.9</v>
       </c>
       <c r="F13" t="n">
         <v>6.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2278</v>
+        <v>0.2291</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2185</v>
+        <v>0.2198</v>
       </c>
       <c r="I13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14973.01</v>
+        <v>14679.08</v>
       </c>
       <c r="E14" t="n">
-        <v>399.3</v>
+        <v>391.4</v>
       </c>
       <c r="F14" t="n">
         <v>6.25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2459</v>
+        <v>0.2488</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2452</v>
+        <v>0.2481</v>
       </c>
       <c r="I14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15313.72</v>
+        <v>14841.01</v>
       </c>
       <c r="E15" t="n">
-        <v>408.4</v>
+        <v>395.8</v>
       </c>
       <c r="F15" t="n">
         <v>6.25</v>
@@ -979,7 +979,7 @@
         <v>0.2515</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2508</v>
+        <v>0.2509</v>
       </c>
       <c r="I15" t="n">
         <v>91</v>
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16722.71</v>
+        <v>16026.84</v>
       </c>
       <c r="E16" t="n">
-        <v>464.5</v>
+        <v>445.2</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2746</v>
+        <v>0.2716</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2853</v>
+        <v>0.2822</v>
       </c>
       <c r="I16" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13891</v>
+        <v>13461.63</v>
       </c>
       <c r="E17" t="n">
-        <v>356.2</v>
+        <v>345.2</v>
       </c>
       <c r="F17" t="n">
         <v>6.5</v>
@@ -1051,10 +1051,10 @@
         <v>0.2281</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2187</v>
+        <v>0.2188</v>
       </c>
       <c r="I17" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1075,22 +1075,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24446.23</v>
+        <v>24799.39</v>
       </c>
       <c r="E18" t="n">
-        <v>814.9</v>
+        <v>826.6</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3178</v>
+        <v>0.3223</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3428</v>
+        <v>0.3473</v>
       </c>
       <c r="I18" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23884.97</v>
+        <v>23963.35</v>
       </c>
       <c r="E19" t="n">
-        <v>796.2</v>
+        <v>798.8</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3105</v>
+        <v>0.3114</v>
       </c>
       <c r="H19" t="n">
-        <v>0.335</v>
+        <v>0.3356</v>
       </c>
       <c r="I19" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15455.38</v>
+        <v>15178.68</v>
       </c>
       <c r="E20" t="n">
-        <v>429.3</v>
+        <v>421.6</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2009</v>
+        <v>0.1973</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1806</v>
+        <v>0.1771</v>
       </c>
       <c r="I20" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13127.37</v>
+        <v>13004.26</v>
       </c>
       <c r="E21" t="n">
-        <v>336.6</v>
+        <v>333.4</v>
       </c>
       <c r="F21" t="n">
         <v>6.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1707</v>
+        <v>0.169</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1416</v>
+        <v>0.1401</v>
       </c>
       <c r="I21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1219,22 +1219,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24479.97</v>
+        <v>24255.2</v>
       </c>
       <c r="E22" t="n">
-        <v>816</v>
+        <v>808.5</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3238</v>
+        <v>0.3184</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3486</v>
+        <v>0.3433</v>
       </c>
       <c r="I22" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23705.27</v>
+        <v>23593.26</v>
       </c>
       <c r="E23" t="n">
-        <v>790.2</v>
+        <v>786.4</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3135</v>
+        <v>0.3097</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3375</v>
+        <v>0.3339</v>
       </c>
       <c r="I23" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14926.91</v>
+        <v>15679.2</v>
       </c>
       <c r="E24" t="n">
-        <v>414.6</v>
+        <v>435.5</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1974</v>
+        <v>0.2058</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1771</v>
+        <v>0.1849</v>
       </c>
       <c r="I24" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12491.28</v>
+        <v>12658.77</v>
       </c>
       <c r="E25" t="n">
-        <v>320.3</v>
+        <v>324.6</v>
       </c>
       <c r="F25" t="n">
         <v>6.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1652</v>
+        <v>0.1662</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1368</v>
+        <v>0.1378</v>
       </c>
       <c r="I25" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24917.6</v>
+        <v>23222.58</v>
       </c>
       <c r="E26" t="n">
-        <v>830.6</v>
+        <v>774.1</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3235</v>
+        <v>0.3057</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3484</v>
+        <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1399,22 +1399,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23830.23</v>
+        <v>24433.37</v>
       </c>
       <c r="E27" t="n">
-        <v>794.3</v>
+        <v>814.4</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3093</v>
+        <v>0.3217</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3332</v>
+        <v>0.3472</v>
       </c>
       <c r="I27" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1435,22 +1435,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15751.58</v>
+        <v>14878.43</v>
       </c>
       <c r="E28" t="n">
-        <v>437.5</v>
+        <v>413.3</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2045</v>
+        <v>0.1959</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1835</v>
+        <v>0.1762</v>
       </c>
       <c r="I28" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1471,22 +1471,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12536.79</v>
+        <v>13419.74</v>
       </c>
       <c r="E29" t="n">
-        <v>321.5</v>
+        <v>344.1</v>
       </c>
       <c r="F29" t="n">
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1627</v>
+        <v>0.1767</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1348</v>
+        <v>0.1467</v>
       </c>
       <c r="I29" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>23110.98</v>
+        <v>24542.64</v>
       </c>
       <c r="E30" t="n">
-        <v>770.4</v>
+        <v>818.1</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3112</v>
+        <v>0.3156</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3355</v>
+        <v>0.3401</v>
       </c>
       <c r="I30" t="n">
         <v>91</v>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23755.59</v>
+        <v>24566.62</v>
       </c>
       <c r="E31" t="n">
-        <v>791.9</v>
+        <v>818.9</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3199</v>
+        <v>0.3159</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3448</v>
+        <v>0.3404</v>
       </c>
       <c r="I31" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1579,19 +1579,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14834.36</v>
+        <v>15939.15</v>
       </c>
       <c r="E32" t="n">
-        <v>412.1</v>
+        <v>442.8</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1998</v>
+        <v>0.205</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1794</v>
+        <v>0.184</v>
       </c>
       <c r="I32" t="n">
         <v>91</v>
@@ -1615,22 +1615,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12562.17</v>
+        <v>12711.66</v>
       </c>
       <c r="E33" t="n">
-        <v>322.1</v>
+        <v>325.9</v>
       </c>
       <c r="F33" t="n">
         <v>6.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1692</v>
+        <v>0.1635</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1403</v>
+        <v>0.1355</v>
       </c>
       <c r="I33" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1651,19 +1651,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12229.85</v>
+        <v>12062.35</v>
       </c>
       <c r="E34" t="n">
-        <v>326.1</v>
+        <v>321.7</v>
       </c>
       <c r="F34" t="n">
         <v>6.25</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2286</v>
+        <v>0.2235</v>
       </c>
       <c r="H34" t="n">
-        <v>0.228</v>
+        <v>0.2229</v>
       </c>
       <c r="I34" t="n">
         <v>91</v>
@@ -1687,22 +1687,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12288.84</v>
+        <v>12069.53</v>
       </c>
       <c r="E35" t="n">
-        <v>327.7</v>
+        <v>321.9</v>
       </c>
       <c r="F35" t="n">
         <v>6.25</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2297</v>
+        <v>0.2237</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2291</v>
+        <v>0.2231</v>
       </c>
       <c r="I35" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1723,22 +1723,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15615.46</v>
+        <v>16155.92</v>
       </c>
       <c r="E36" t="n">
-        <v>433.8</v>
+        <v>448.8</v>
       </c>
       <c r="F36" t="n">
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2919</v>
+        <v>0.2994</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3033</v>
+        <v>0.311</v>
       </c>
       <c r="I36" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1759,19 +1759,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13360.11</v>
+        <v>13674.71</v>
       </c>
       <c r="E37" t="n">
-        <v>342.6</v>
+        <v>350.6</v>
       </c>
       <c r="F37" t="n">
         <v>6.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2497</v>
+        <v>0.2534</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2395</v>
+        <v>0.243</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1795,19 +1795,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12170.2</v>
+        <v>12413.99</v>
       </c>
       <c r="E38" t="n">
-        <v>324.5</v>
+        <v>331</v>
       </c>
       <c r="F38" t="n">
         <v>6.25</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2259</v>
+        <v>0.2344</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2254</v>
+        <v>0.2338</v>
       </c>
       <c r="I38" t="n">
         <v>91</v>
@@ -1831,22 +1831,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11548.42</v>
+        <v>11634.94</v>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>310.3</v>
       </c>
       <c r="F39" t="n">
         <v>6.25</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2144</v>
+        <v>0.2197</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2139</v>
+        <v>0.2191</v>
       </c>
       <c r="I39" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -1867,22 +1867,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16072.16</v>
+        <v>15703.77</v>
       </c>
       <c r="E40" t="n">
-        <v>446.4</v>
+        <v>436.2</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2983</v>
+        <v>0.2966</v>
       </c>
       <c r="H40" t="n">
-        <v>0.31</v>
+        <v>0.3081</v>
       </c>
       <c r="I40" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14082.03</v>
+        <v>13199.78</v>
       </c>
       <c r="E41" t="n">
-        <v>361.1</v>
+        <v>338.5</v>
       </c>
       <c r="F41" t="n">
         <v>6.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2614</v>
+        <v>0.2493</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2507</v>
+        <v>0.239</v>
       </c>
       <c r="I41" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12339.21</v>
+        <v>11840.29</v>
       </c>
       <c r="E42" t="n">
-        <v>329</v>
+        <v>315.7</v>
       </c>
       <c r="F42" t="n">
         <v>6.25</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2285</v>
+        <v>0.2186</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2278</v>
+        <v>0.2179</v>
       </c>
       <c r="I42" t="n">
         <v>89</v>
@@ -1975,22 +1975,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11806.99</v>
+        <v>12382.43</v>
       </c>
       <c r="E43" t="n">
-        <v>314.9</v>
+        <v>330.2</v>
       </c>
       <c r="F43" t="n">
         <v>6.25</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2186</v>
+        <v>0.2286</v>
       </c>
       <c r="H43" t="n">
-        <v>0.218</v>
+        <v>0.2279</v>
       </c>
       <c r="I43" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16317.06</v>
+        <v>16540.24</v>
       </c>
       <c r="E44" t="n">
-        <v>453.3</v>
+        <v>459.5</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3022</v>
+        <v>0.3054</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3138</v>
+        <v>0.3171</v>
       </c>
       <c r="I44" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2047,19 +2047,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13537.46</v>
+        <v>13399.42</v>
       </c>
       <c r="E45" t="n">
-        <v>347.1</v>
+        <v>343.6</v>
       </c>
       <c r="F45" t="n">
         <v>6.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2507</v>
+        <v>0.2474</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2403</v>
+        <v>0.2371</v>
       </c>
       <c r="I45" t="n">
         <v>88</v>
@@ -2083,22 +2083,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11848.25</v>
+        <v>12418.68</v>
       </c>
       <c r="E46" t="n">
-        <v>316</v>
+        <v>331.2</v>
       </c>
       <c r="F46" t="n">
         <v>6.25</v>
       </c>
       <c r="G46" t="n">
-        <v>0.216</v>
+        <v>0.2287</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2154</v>
+        <v>0.2281</v>
       </c>
       <c r="I46" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2119,22 +2119,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12208.93</v>
+        <v>11940.39</v>
       </c>
       <c r="E47" t="n">
-        <v>325.6</v>
+        <v>318.4</v>
       </c>
       <c r="F47" t="n">
         <v>6.25</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2226</v>
+        <v>0.2199</v>
       </c>
       <c r="H47" t="n">
-        <v>0.222</v>
+        <v>0.2193</v>
       </c>
       <c r="I47" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2155,22 +2155,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16598.43</v>
+        <v>16048.78</v>
       </c>
       <c r="E48" t="n">
-        <v>461.1</v>
+        <v>445.8</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3026</v>
+        <v>0.2955</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3144</v>
+        <v>0.3071</v>
       </c>
       <c r="I48" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14194.63</v>
+        <v>13900.82</v>
       </c>
       <c r="E49" t="n">
-        <v>364</v>
+        <v>356.4</v>
       </c>
       <c r="F49" t="n">
         <v>6.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2588</v>
+        <v>0.256</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2482</v>
+        <v>0.2455</v>
       </c>
       <c r="I49" t="n">
         <v>90</v>
@@ -2227,22 +2227,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12477.68</v>
+        <v>11881.31</v>
       </c>
       <c r="E50" t="n">
-        <v>332.7</v>
+        <v>316.8</v>
       </c>
       <c r="F50" t="n">
         <v>6.25</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2288</v>
+        <v>0.2161</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2282</v>
+        <v>0.2156</v>
       </c>
       <c r="I50" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12192.85</v>
+        <v>12467.17</v>
       </c>
       <c r="E51" t="n">
-        <v>325.1</v>
+        <v>332.5</v>
       </c>
       <c r="F51" t="n">
         <v>6.25</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2236</v>
+        <v>0.2268</v>
       </c>
       <c r="H51" t="n">
-        <v>0.223</v>
+        <v>0.2262</v>
       </c>
       <c r="I51" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2299,22 +2299,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16323.4</v>
+        <v>16482.22</v>
       </c>
       <c r="E52" t="n">
-        <v>453.4</v>
+        <v>457.8</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2994</v>
+        <v>0.2998</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3109</v>
+        <v>0.3115</v>
       </c>
       <c r="I52" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13532.47</v>
+        <v>14142.7</v>
       </c>
       <c r="E53" t="n">
-        <v>347</v>
+        <v>362.6</v>
       </c>
       <c r="F53" t="n">
         <v>6.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2482</v>
+        <v>0.2573</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2379</v>
+        <v>0.2467</v>
       </c>
       <c r="I53" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2371,22 +2371,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11584.48</v>
+        <v>12084.73</v>
       </c>
       <c r="E54" t="n">
-        <v>308.9</v>
+        <v>322.3</v>
       </c>
       <c r="F54" t="n">
         <v>6.25</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2208</v>
+        <v>0.2262</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2202</v>
+        <v>0.2256</v>
       </c>
       <c r="I54" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11713.9</v>
+        <v>12178.65</v>
       </c>
       <c r="E55" t="n">
-        <v>312.4</v>
+        <v>324.8</v>
       </c>
       <c r="F55" t="n">
         <v>6.25</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2232</v>
+        <v>0.2279</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2227</v>
+        <v>0.2274</v>
       </c>
       <c r="I55" t="n">
         <v>89</v>
@@ -2443,19 +2443,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15574.9</v>
+        <v>15567.94</v>
       </c>
       <c r="E56" t="n">
-        <v>432.6</v>
+        <v>432.4</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2968</v>
+        <v>0.2914</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3084</v>
+        <v>0.3028</v>
       </c>
       <c r="I56" t="n">
         <v>90</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13598.98</v>
+        <v>13600.12</v>
       </c>
       <c r="E57" t="n">
         <v>348.7</v>
@@ -2488,13 +2488,13 @@
         <v>6.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2592</v>
+        <v>0.2545</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2486</v>
+        <v>0.2442</v>
       </c>
       <c r="I57" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2515,22 +2515,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12241.88</v>
+        <v>11809.85</v>
       </c>
       <c r="E58" t="n">
-        <v>326.5</v>
+        <v>314.9</v>
       </c>
       <c r="F58" t="n">
         <v>6.25</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2255</v>
+        <v>0.2187</v>
       </c>
       <c r="H58" t="n">
-        <v>0.225</v>
+        <v>0.218</v>
       </c>
       <c r="I58" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2551,22 +2551,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12039.22</v>
+        <v>12401.7</v>
       </c>
       <c r="E59" t="n">
-        <v>321</v>
+        <v>330.7</v>
       </c>
       <c r="F59" t="n">
         <v>6.25</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2218</v>
+        <v>0.2297</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2213</v>
+        <v>0.2289</v>
       </c>
       <c r="I59" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2587,22 +2587,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15920.76</v>
+        <v>16564.56</v>
       </c>
       <c r="E60" t="n">
-        <v>442.2</v>
+        <v>460.1</v>
       </c>
       <c r="F60" t="n">
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2933</v>
+        <v>0.3067</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3048</v>
+        <v>0.3185</v>
       </c>
       <c r="I60" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14083.52</v>
+        <v>13224.76</v>
       </c>
       <c r="E61" t="n">
-        <v>361.1</v>
+        <v>339.1</v>
       </c>
       <c r="F61" t="n">
         <v>6.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2594</v>
+        <v>0.2449</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2489</v>
+        <v>0.2347</v>
       </c>
       <c r="I61" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2659,22 +2659,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12232.63</v>
+        <v>11622.16</v>
       </c>
       <c r="E62" t="n">
-        <v>326.2</v>
+        <v>309.9</v>
       </c>
       <c r="F62" t="n">
         <v>6.25</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2259</v>
+        <v>0.2139</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2252</v>
+        <v>0.2133</v>
       </c>
       <c r="I62" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -2695,22 +2695,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12087.12</v>
+        <v>12479.14</v>
       </c>
       <c r="E63" t="n">
-        <v>322.3</v>
+        <v>332.8</v>
       </c>
       <c r="F63" t="n">
         <v>6.25</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2232</v>
+        <v>0.2297</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2225</v>
+        <v>0.229</v>
       </c>
       <c r="I63" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -2731,19 +2731,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16398.86</v>
+        <v>16414.73</v>
       </c>
       <c r="E64" t="n">
-        <v>455.5</v>
+        <v>456</v>
       </c>
       <c r="F64" t="n">
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3028</v>
+        <v>0.3021</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3145</v>
+        <v>0.3138</v>
       </c>
       <c r="I64" t="n">
         <v>88</v>
@@ -2767,22 +2767,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13430.93</v>
+        <v>13813.94</v>
       </c>
       <c r="E65" t="n">
-        <v>344.4</v>
+        <v>354.2</v>
       </c>
       <c r="F65" t="n">
         <v>6.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0.248</v>
+        <v>0.2543</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2378</v>
+        <v>0.2438</v>
       </c>
       <c r="I65" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>

--- a/stella/test_fixtures/inventory_risk/iri_data.xlsx
+++ b/stella/test_fixtures/inventory_risk/iri_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,23 +495,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15028.5</v>
+        <v>16648.35</v>
       </c>
       <c r="E2" t="n">
-        <v>400.8</v>
+        <v>2646.8</v>
       </c>
       <c r="F2" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2532</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2525</v>
+        <v>0.0519</v>
       </c>
       <c r="I2" t="n">
         <v>92</v>
@@ -531,26 +531,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14522.01</v>
+        <v>17154.19</v>
       </c>
       <c r="E3" t="n">
-        <v>387.3</v>
+        <v>2727.2</v>
       </c>
       <c r="F3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2447</v>
+        <v>0.0746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439</v>
+        <v>0.0535</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -562,31 +562,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16632.16</v>
+        <v>17913.5</v>
       </c>
       <c r="E4" t="n">
-        <v>462</v>
+        <v>2847.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2803</v>
+        <v>0.0779</v>
       </c>
       <c r="H4" t="n">
-        <v>0.291</v>
+        <v>0.0558</v>
       </c>
       <c r="I4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -598,31 +598,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13160.74</v>
+        <v>15485.62</v>
       </c>
       <c r="E5" t="n">
-        <v>337.5</v>
+        <v>2386.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2218</v>
+        <v>0.0673</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2126</v>
+        <v>0.0468</v>
       </c>
       <c r="I5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -630,35 +630,35 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15575.48</v>
+        <v>16383.63</v>
       </c>
       <c r="E6" t="n">
-        <v>415.3</v>
+        <v>2524.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2541</v>
+        <v>0.0712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2534</v>
+        <v>0.0495</v>
       </c>
       <c r="I6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15362.43</v>
+        <v>15751.28</v>
       </c>
       <c r="E7" t="n">
-        <v>409.7</v>
+        <v>2427</v>
       </c>
       <c r="F7" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2506</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2499</v>
+        <v>0.0476</v>
       </c>
       <c r="I7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -702,32 +702,32 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16562.2</v>
+        <v>17000.91</v>
       </c>
       <c r="E8" t="n">
-        <v>460.1</v>
+        <v>3962.9</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2702</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2807</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>90</v>
@@ -738,35 +738,35 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13805.59</v>
+        <v>16841.63</v>
       </c>
       <c r="E9" t="n">
-        <v>354</v>
+        <v>3925.8</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2252</v>
+        <v>0.0732</v>
       </c>
       <c r="H9" t="n">
-        <v>0.216</v>
+        <v>0.077</v>
       </c>
       <c r="I9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -774,32 +774,32 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15429.09</v>
+        <v>17026.14</v>
       </c>
       <c r="E10" t="n">
-        <v>411.4</v>
+        <v>3968.8</v>
       </c>
       <c r="F10" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2561</v>
+        <v>0.074</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2556</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>89</v>
@@ -810,35 +810,35 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14955.36</v>
+        <v>14289.46</v>
       </c>
       <c r="E11" t="n">
-        <v>398.8</v>
+        <v>3493.8</v>
       </c>
       <c r="F11" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2483</v>
+        <v>0.0621</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2477</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -846,35 +846,35 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16051.08</v>
+        <v>14658.35</v>
       </c>
       <c r="E12" t="n">
-        <v>445.9</v>
+        <v>3583.9</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2665</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2769</v>
+        <v>0.0703</v>
       </c>
       <c r="I12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -882,35 +882,35 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13802.4</v>
+        <v>14948.42</v>
       </c>
       <c r="E13" t="n">
-        <v>353.9</v>
+        <v>3654.9</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2291</v>
+        <v>0.065</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2198</v>
+        <v>0.0717</v>
       </c>
       <c r="I13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14679.08</v>
+        <v>12026.26</v>
       </c>
       <c r="E14" t="n">
-        <v>391.4</v>
+        <v>4310.5</v>
       </c>
       <c r="F14" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2488</v>
+        <v>0.0523</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2481</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -954,35 +954,35 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14841.01</v>
+        <v>12011.57</v>
       </c>
       <c r="E15" t="n">
-        <v>395.8</v>
+        <v>4305.2</v>
       </c>
       <c r="F15" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2515</v>
+        <v>0.0522</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2509</v>
+        <v>0.0844</v>
       </c>
       <c r="I15" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -990,35 +990,35 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16026.84</v>
+        <v>11811.66</v>
       </c>
       <c r="E16" t="n">
-        <v>445.2</v>
+        <v>4233.6</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2716</v>
+        <v>0.0514</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2822</v>
+        <v>0.083</v>
       </c>
       <c r="I16" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45682</v>
+        <v>45668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13461.63</v>
+        <v>17855.02</v>
       </c>
       <c r="E17" t="n">
-        <v>345.2</v>
+        <v>2838.6</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2281</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2188</v>
+        <v>0.0556</v>
       </c>
       <c r="I17" t="n">
         <v>92</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1071,34 +1071,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24799.39</v>
+        <v>17881.32</v>
       </c>
       <c r="E18" t="n">
-        <v>826.6</v>
+        <v>2842.8</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3223</v>
+        <v>0.0779</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3473</v>
+        <v>0.0557</v>
       </c>
       <c r="I18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1107,59 +1107,59 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23963.35</v>
+        <v>17065.25</v>
       </c>
       <c r="E19" t="n">
-        <v>798.8</v>
+        <v>2713.1</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3114</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3356</v>
+        <v>0.0532</v>
       </c>
       <c r="I19" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15178.68</v>
+        <v>15637.58</v>
       </c>
       <c r="E20" t="n">
-        <v>421.6</v>
+        <v>2409.5</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1973</v>
+        <v>0.0682</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1771</v>
+        <v>0.0472</v>
       </c>
       <c r="I20" t="n">
         <v>91</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13004.26</v>
+        <v>15692.37</v>
       </c>
       <c r="E21" t="n">
-        <v>333.4</v>
+        <v>2417.9</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.169</v>
+        <v>0.0684</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1401</v>
+        <v>0.0474</v>
       </c>
       <c r="I21" t="n">
         <v>90</v>
@@ -1206,104 +1206,104 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24255.2</v>
+        <v>15535.89</v>
       </c>
       <c r="E22" t="n">
-        <v>808.5</v>
+        <v>2393.8</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3184</v>
+        <v>0.0677</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3433</v>
+        <v>0.0469</v>
       </c>
       <c r="I22" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23593.26</v>
+        <v>16014.54</v>
       </c>
       <c r="E23" t="n">
-        <v>786.4</v>
+        <v>3733</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3097</v>
+        <v>0.0698</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3339</v>
+        <v>0.0732</v>
       </c>
       <c r="I23" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15679.2</v>
+        <v>15950.06</v>
       </c>
       <c r="E24" t="n">
-        <v>435.5</v>
+        <v>3718</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2058</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1849</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>88</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12658.77</v>
+        <v>17163.71</v>
       </c>
       <c r="E25" t="n">
-        <v>324.6</v>
+        <v>4000.9</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1662</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1378</v>
+        <v>0.0784</v>
       </c>
       <c r="I25" t="n">
         <v>91</v>
@@ -1350,107 +1350,107 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23222.58</v>
+        <v>14123.51</v>
       </c>
       <c r="E26" t="n">
-        <v>774.1</v>
+        <v>3453.2</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3057</v>
+        <v>0.0616</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33</v>
+        <v>0.0677</v>
       </c>
       <c r="I26" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24433.37</v>
+        <v>14191.92</v>
       </c>
       <c r="E27" t="n">
-        <v>814.4</v>
+        <v>3469.9</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3217</v>
+        <v>0.0619</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3472</v>
+        <v>0.068</v>
       </c>
       <c r="I27" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14878.43</v>
+        <v>15004.55</v>
       </c>
       <c r="E28" t="n">
-        <v>413.3</v>
+        <v>3668.6</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1959</v>
+        <v>0.0654</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1762</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1458,35 +1458,35 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13419.74</v>
+        <v>12354.8</v>
       </c>
       <c r="E29" t="n">
-        <v>344.1</v>
+        <v>4428.2</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1767</v>
+        <v>0.0539</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1467</v>
+        <v>0.0868</v>
       </c>
       <c r="I29" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1494,104 +1494,104 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>24542.64</v>
+        <v>12545.5</v>
       </c>
       <c r="E30" t="n">
-        <v>818.1</v>
+        <v>4496.6</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3156</v>
+        <v>0.0547</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3401</v>
+        <v>0.0881</v>
       </c>
       <c r="I30" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24566.62</v>
+        <v>12404.57</v>
       </c>
       <c r="E31" t="n">
-        <v>818.9</v>
+        <v>4446.1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3159</v>
+        <v>0.0541</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3404</v>
+        <v>0.0871</v>
       </c>
       <c r="I31" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15939.15</v>
+        <v>17790.7</v>
       </c>
       <c r="E32" t="n">
-        <v>442.8</v>
+        <v>2828.4</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.205</v>
+        <v>0.0772</v>
       </c>
       <c r="H32" t="n">
-        <v>0.184</v>
+        <v>0.0553</v>
       </c>
       <c r="I32" t="n">
         <v>91</v>
@@ -1602,35 +1602,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12711.66</v>
+        <v>16713.18</v>
       </c>
       <c r="E33" t="n">
-        <v>325.9</v>
+        <v>2657.1</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1635</v>
+        <v>0.0725</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1355</v>
+        <v>0.0519</v>
       </c>
       <c r="I33" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12062.35</v>
+        <v>17664.24</v>
       </c>
       <c r="E34" t="n">
-        <v>321.7</v>
+        <v>2808.3</v>
       </c>
       <c r="F34" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2235</v>
+        <v>0.0767</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2229</v>
+        <v>0.0549</v>
       </c>
       <c r="I34" t="n">
         <v>91</v>
@@ -1674,35 +1674,35 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12069.53</v>
+        <v>15815.6</v>
       </c>
       <c r="E35" t="n">
-        <v>321.9</v>
+        <v>2436.9</v>
       </c>
       <c r="F35" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2237</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2231</v>
+        <v>0.0476</v>
       </c>
       <c r="I35" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1710,32 +1710,32 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16155.92</v>
+        <v>15698.6</v>
       </c>
       <c r="E36" t="n">
-        <v>448.8</v>
+        <v>2418.9</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2994</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.311</v>
+        <v>0.0473</v>
       </c>
       <c r="I36" t="n">
         <v>90</v>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13674.71</v>
+        <v>16305.49</v>
       </c>
       <c r="E37" t="n">
-        <v>350.6</v>
+        <v>2512.4</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2534</v>
+        <v>0.0708</v>
       </c>
       <c r="H37" t="n">
-        <v>0.243</v>
+        <v>0.0491</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1782,35 +1782,35 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12413.99</v>
+        <v>17057.97</v>
       </c>
       <c r="E38" t="n">
-        <v>331</v>
+        <v>3976.2</v>
       </c>
       <c r="F38" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2344</v>
+        <v>0.074</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2338</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1818,35 +1818,35 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11634.94</v>
+        <v>16245.65</v>
       </c>
       <c r="E39" t="n">
-        <v>310.3</v>
+        <v>3786.9</v>
       </c>
       <c r="F39" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2197</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2191</v>
+        <v>0.074</v>
       </c>
       <c r="I39" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -1854,35 +1854,35 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15703.77</v>
+        <v>16607.45</v>
       </c>
       <c r="E40" t="n">
-        <v>436.2</v>
+        <v>3871.2</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2966</v>
+        <v>0.0721</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3081</v>
+        <v>0.0757</v>
       </c>
       <c r="I40" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13199.78</v>
+        <v>14375.91</v>
       </c>
       <c r="E41" t="n">
-        <v>338.5</v>
+        <v>3514.9</v>
       </c>
       <c r="F41" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2493</v>
+        <v>0.0624</v>
       </c>
       <c r="H41" t="n">
-        <v>0.239</v>
+        <v>0.0687</v>
       </c>
       <c r="I41" t="n">
         <v>91</v>
@@ -1926,32 +1926,32 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11840.29</v>
+        <v>14685.25</v>
       </c>
       <c r="E42" t="n">
-        <v>315.7</v>
+        <v>3590.5</v>
       </c>
       <c r="F42" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2186</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2179</v>
+        <v>0.0702</v>
       </c>
       <c r="I42" t="n">
         <v>89</v>
@@ -1962,35 +1962,35 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12382.43</v>
+        <v>14764.3</v>
       </c>
       <c r="E43" t="n">
-        <v>330.2</v>
+        <v>3609.9</v>
       </c>
       <c r="F43" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2286</v>
+        <v>0.0641</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2279</v>
+        <v>0.0706</v>
       </c>
       <c r="I43" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -1998,35 +1998,35 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16540.24</v>
+        <v>12384.36</v>
       </c>
       <c r="E44" t="n">
-        <v>459.5</v>
+        <v>4438.8</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3054</v>
+        <v>0.0537</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3171</v>
+        <v>0.0868</v>
       </c>
       <c r="I44" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2034,35 +2034,35 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13399.42</v>
+        <v>12397.33</v>
       </c>
       <c r="E45" t="n">
-        <v>343.6</v>
+        <v>4443.5</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2474</v>
+        <v>0.0538</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2371</v>
+        <v>0.0868</v>
       </c>
       <c r="I45" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2070,32 +2070,32 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45738</v>
+        <v>45675</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12418.68</v>
+        <v>11917.62</v>
       </c>
       <c r="E46" t="n">
-        <v>331.2</v>
+        <v>4271.5</v>
       </c>
       <c r="F46" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2287</v>
+        <v>0.0517</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2281</v>
+        <v>0.0835</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2115,26 +2115,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11940.39</v>
+        <v>17296.38</v>
       </c>
       <c r="E47" t="n">
-        <v>318.4</v>
+        <v>2749.8</v>
       </c>
       <c r="F47" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2199</v>
+        <v>0.0746</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2193</v>
+        <v>0.0534</v>
       </c>
       <c r="I47" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2142,35 +2142,35 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16048.78</v>
+        <v>17463.17</v>
       </c>
       <c r="E48" t="n">
-        <v>445.8</v>
+        <v>2776.3</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2955</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3071</v>
+        <v>0.0539</v>
       </c>
       <c r="I48" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2178,35 +2178,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13900.82</v>
+        <v>17889.73</v>
       </c>
       <c r="E49" t="n">
-        <v>356.4</v>
+        <v>2844.2</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.256</v>
+        <v>0.0772</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2455</v>
+        <v>0.0552</v>
       </c>
       <c r="I49" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2214,32 +2214,32 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11881.31</v>
+        <v>16052.23</v>
       </c>
       <c r="E50" t="n">
-        <v>316.8</v>
+        <v>2473.4</v>
       </c>
       <c r="F50" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2161</v>
+        <v>0.0692</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2156</v>
+        <v>0.048</v>
       </c>
       <c r="I50" t="n">
         <v>88</v>
@@ -2250,35 +2250,35 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12467.17</v>
+        <v>16099.58</v>
       </c>
       <c r="E51" t="n">
-        <v>332.5</v>
+        <v>2480.7</v>
       </c>
       <c r="F51" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2268</v>
+        <v>0.0694</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2262</v>
+        <v>0.0482</v>
       </c>
       <c r="I51" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2286,32 +2286,32 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16482.22</v>
+        <v>16193.82</v>
       </c>
       <c r="E52" t="n">
-        <v>457.8</v>
+        <v>2495.2</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2998</v>
+        <v>0.0698</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3115</v>
+        <v>0.0485</v>
       </c>
       <c r="I52" t="n">
         <v>91</v>
@@ -2322,35 +2322,35 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14142.7</v>
+        <v>16830.33</v>
       </c>
       <c r="E53" t="n">
-        <v>362.6</v>
+        <v>3923.2</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2573</v>
+        <v>0.0726</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2467</v>
+        <v>0.0762</v>
       </c>
       <c r="I53" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2358,35 +2358,35 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12084.73</v>
+        <v>15950.78</v>
       </c>
       <c r="E54" t="n">
-        <v>322.3</v>
+        <v>3718.1</v>
       </c>
       <c r="F54" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2262</v>
+        <v>0.0688</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2256</v>
+        <v>0.0722</v>
       </c>
       <c r="I54" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2394,35 +2394,35 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12178.65</v>
+        <v>16537.23</v>
       </c>
       <c r="E55" t="n">
-        <v>324.8</v>
+        <v>3854.8</v>
       </c>
       <c r="F55" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2279</v>
+        <v>0.0713</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2274</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2430,35 +2430,35 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15567.94</v>
+        <v>14600.22</v>
       </c>
       <c r="E56" t="n">
-        <v>432.4</v>
+        <v>3569.7</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2914</v>
+        <v>0.063</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3028</v>
+        <v>0.0693</v>
       </c>
       <c r="I56" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2466,35 +2466,35 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13600.12</v>
+        <v>15115.01</v>
       </c>
       <c r="E57" t="n">
-        <v>348.7</v>
+        <v>3695.6</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2545</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2442</v>
+        <v>0.0718</v>
       </c>
       <c r="I57" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2502,35 +2502,35 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11809.85</v>
+        <v>14614.15</v>
       </c>
       <c r="E58" t="n">
-        <v>314.9</v>
+        <v>3573.1</v>
       </c>
       <c r="F58" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2187</v>
+        <v>0.063</v>
       </c>
       <c r="H58" t="n">
-        <v>0.218</v>
+        <v>0.0694</v>
       </c>
       <c r="I58" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2538,35 +2538,35 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12401.7</v>
+        <v>12244.89</v>
       </c>
       <c r="E59" t="n">
-        <v>330.7</v>
+        <v>4388.8</v>
       </c>
       <c r="F59" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2297</v>
+        <v>0.0528</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2289</v>
+        <v>0.0852</v>
       </c>
       <c r="I59" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2574,32 +2574,32 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16564.56</v>
+        <v>12729.92</v>
       </c>
       <c r="E60" t="n">
-        <v>460.1</v>
+        <v>4562.7</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3067</v>
+        <v>0.0549</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3185</v>
+        <v>0.0886</v>
       </c>
       <c r="I60" t="n">
         <v>89</v>
@@ -2610,35 +2610,35 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13224.76</v>
+        <v>12227.46</v>
       </c>
       <c r="E61" t="n">
-        <v>339.1</v>
+        <v>4382.6</v>
       </c>
       <c r="F61" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2449</v>
+        <v>0.0527</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2347</v>
+        <v>0.0851</v>
       </c>
       <c r="I61" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11622.16</v>
+        <v>27525.42</v>
       </c>
       <c r="E62" t="n">
-        <v>309.9</v>
+        <v>5461.4</v>
       </c>
       <c r="F62" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2139</v>
+        <v>0.1081</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2133</v>
+        <v>0.0939</v>
       </c>
       <c r="I62" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2691,100 +2691,6436 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12479.14</v>
+        <v>28295.78</v>
       </c>
       <c r="E63" t="n">
-        <v>332.8</v>
+        <v>5614.2</v>
       </c>
       <c r="F63" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2297</v>
+        <v>0.1111</v>
       </c>
       <c r="H63" t="n">
-        <v>0.229</v>
+        <v>0.0965</v>
       </c>
       <c r="I63" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16414.73</v>
+        <v>27122.75</v>
       </c>
       <c r="E64" t="n">
-        <v>456</v>
+        <v>5381.5</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3021</v>
+        <v>0.1065</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3138</v>
+        <v>0.0925</v>
       </c>
       <c r="I64" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>14925.78</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2299.8</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="I65" t="n">
+        <v>92</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>14456.72</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2227.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="I66" t="n">
+        <v>89</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>14752.65</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2273.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="I67" t="n">
+        <v>90</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>16299.46</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3799.4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="I68" t="n">
+        <v>92</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>16488.59</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3843.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="I69" t="n">
+        <v>89</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>15505.67</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3614.4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="I70" t="n">
+        <v>90</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13941.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3408.6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="I71" t="n">
+        <v>92</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13899.93</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3398.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="I72" t="n">
+        <v>92</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13914.04</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3402</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="I73" t="n">
+        <v>92</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12233.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4384.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>91</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12633.07</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4528</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+      <c r="I75" t="n">
+        <v>89</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12629.92</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4526.9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>89</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>27824.85</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5520.8</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="I77" t="n">
+        <v>87</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>27854.78</v>
+      </c>
+      <c r="E78" t="n">
+        <v>5526.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="I78" t="n">
+        <v>89</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>27732.2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5502.4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="I79" t="n">
+        <v>88</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14614.54</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2251.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="I80" t="n">
+        <v>91</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>14350.45</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2211.2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="I81" t="n">
+        <v>89</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>14744.65</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2271.9</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="I82" t="n">
+        <v>88</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>15644.7</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3646.8</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="I83" t="n">
+        <v>88</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15641.06</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3645.9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="I84" t="n">
+        <v>90</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>15382.99</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3585.8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="I85" t="n">
+        <v>88</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13829.9</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3381.4</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="I86" t="n">
+        <v>92</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>14580.82</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3565</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="I87" t="n">
+        <v>88</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>14122.15</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3452.8</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="I88" t="n">
+        <v>91</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11888.66</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4261.2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="I89" t="n">
+        <v>90</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12405.39</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4446.4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="I90" t="n">
+        <v>90</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12205.72</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4374.8</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="I91" t="n">
+        <v>88</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>28391.38</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5633.2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="I92" t="n">
+        <v>89</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>28591.63</v>
+      </c>
+      <c r="E93" t="n">
+        <v>5672.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="I93" t="n">
+        <v>88</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>26635.63</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5284.8</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="I94" t="n">
+        <v>87</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>14084.77</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2170.2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="I95" t="n">
+        <v>89</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>14923.6</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2299.5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="I96" t="n">
+        <v>91</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>14513.72</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2236.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="I97" t="n">
+        <v>88</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>15411.93</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3592.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="I98" t="n">
+        <v>90</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15478.84</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3608.1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="I99" t="n">
+        <v>91</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>16058.78</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3743.3</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="I100" t="n">
+        <v>91</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>14438.19</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3530.1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I101" t="n">
+        <v>91</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>14295.91</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3495.3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="I102" t="n">
+        <v>91</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>14697.26</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3593.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="I103" t="n">
+        <v>91</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12147.47</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4353.9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="I104" t="n">
+        <v>88</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11959.05</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4286.4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="I105" t="n">
+        <v>90</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12131.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4348.1</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="I106" t="n">
+        <v>90</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>27155.77</v>
+      </c>
+      <c r="E107" t="n">
+        <v>5388</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="I107" t="n">
+        <v>93</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>26705.56</v>
+      </c>
+      <c r="E108" t="n">
+        <v>5298.7</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="I108" t="n">
+        <v>93</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>27107.03</v>
+      </c>
+      <c r="E109" t="n">
+        <v>5378.4</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="I109" t="n">
+        <v>93</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>14404.31</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2219.5</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="I110" t="n">
+        <v>90</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>14356.93</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2212.2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="I111" t="n">
+        <v>88</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>14082.53</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2169.9</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="I112" t="n">
+        <v>92</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>16267.35</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3791.9</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="I113" t="n">
+        <v>91</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>16395.81</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3821.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="I114" t="n">
+        <v>91</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>15477.01</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3607.7</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="I115" t="n">
+        <v>90</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>14670.51</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3586.9</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="I116" t="n">
+        <v>90</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>13636.04</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3334</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="I117" t="n">
+        <v>88</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>14665.28</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3585.6</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>91</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12592.63</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4513.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="I119" t="n">
+        <v>88</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11678.83</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4186</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="I120" t="n">
+        <v>91</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12408.96</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4447.7</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="I121" t="n">
+        <v>92</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>13807.52</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2195.2</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="I122" t="n">
+        <v>89</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>13848.88</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2201.7</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="I123" t="n">
+        <v>91</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>13630.11</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2166.9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="I124" t="n">
+        <v>92</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>16666.01</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2568</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="I125" t="n">
+        <v>89</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>16362.32</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2521.2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="I126" t="n">
+        <v>91</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15894.4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2449.1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="I127" t="n">
+        <v>92</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>16086.82</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3749.8</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="I128" t="n">
+        <v>88</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>16145.97</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3763.6</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="I129" t="n">
+        <v>88</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>16468.83</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3838.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="I130" t="n">
+        <v>91</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>15139.44</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3701.6</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="I131" t="n">
+        <v>89</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>14895.64</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3642</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="I132" t="n">
+        <v>88</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>14288.66</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3493.6</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="I133" t="n">
+        <v>90</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12629.12</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4526.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="I134" t="n">
+        <v>91</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12156.38</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4357.1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="I135" t="n">
+        <v>89</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12621.42</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4523.8</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="I136" t="n">
+        <v>89</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>14576.22</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2317.4</v>
+      </c>
+      <c r="F137" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="I137" t="n">
+        <v>90</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>14206.73</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2258.6</v>
+      </c>
+      <c r="F138" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="I138" t="n">
+        <v>90</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>14572.85</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2316.8</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="I139" t="n">
+        <v>90</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>15993.86</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2464.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I140" t="n">
+        <v>89</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>16644.83</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2564.7</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="I141" t="n">
+        <v>88</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>16256.52</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2504.9</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="I142" t="n">
+        <v>91</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>16008.98</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3731.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="I143" t="n">
+        <v>89</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>17025.33</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3968.6</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="I144" t="n">
+        <v>91</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>16502.32</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3846.7</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.0747</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="I145" t="n">
+        <v>88</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>14202.56</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3472.5</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="I146" t="n">
+        <v>88</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>14215.49</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3475.7</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="I147" t="n">
+        <v>89</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>14841.12</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3628.6</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="I148" t="n">
+        <v>90</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11831.48</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4240.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="I149" t="n">
+        <v>89</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>12066.42</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4324.9</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="I150" t="n">
+        <v>91</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11922.24</v>
+      </c>
+      <c r="E151" t="n">
+        <v>4273.2</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="I151" t="n">
+        <v>89</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>14565.28</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2315.6</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="I152" t="n">
+        <v>92</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>14638.6</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2327.3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="I153" t="n">
+        <v>92</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>13974.08</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2221.6</v>
+      </c>
+      <c r="F154" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="I154" t="n">
+        <v>88</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>16082.2</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2478</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="I155" t="n">
+        <v>90</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>15863.36</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2444.3</v>
+      </c>
+      <c r="F156" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I156" t="n">
+        <v>90</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>15961.59</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2459.4</v>
+      </c>
+      <c r="F157" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="I157" t="n">
+        <v>88</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>15988.35</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3726.9</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0747</v>
+      </c>
+      <c r="I158" t="n">
+        <v>89</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>16890.2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3937.1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="I159" t="n">
+        <v>92</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>17101.06</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3986.3</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="I160" t="n">
+        <v>88</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>14062.93</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3438.4</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="I161" t="n">
+        <v>90</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>14740.33</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3604</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="I162" t="n">
+        <v>92</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>14930.38</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3650.5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="I163" t="n">
+        <v>89</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>12064.66</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4324.3</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="I164" t="n">
+        <v>90</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>12558.4</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4501.2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="I165" t="n">
+        <v>92</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>12405.98</v>
+      </c>
+      <c r="E166" t="n">
+        <v>4446.6</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="I166" t="n">
+        <v>90</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>14436.62</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2295.2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="I167" t="n">
+        <v>92</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>14342.37</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2280.2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="I168" t="n">
+        <v>89</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>15405.93</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2449.3</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I169" t="n">
+        <v>90</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>15761.81</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2428.6</v>
+      </c>
+      <c r="F170" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="I170" t="n">
+        <v>92</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>16067.97</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2475.8</v>
+      </c>
+      <c r="F171" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="I171" t="n">
+        <v>88</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>15536.79</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2394</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="I172" t="n">
+        <v>89</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>16415.62</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3826.5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="I173" t="n">
+        <v>88</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>17084.81</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3982.5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="I174" t="n">
+        <v>89</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>16519.69</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3850.7</v>
+      </c>
+      <c r="F175" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I175" t="n">
+        <v>89</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>15172.86</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3709.7</v>
+      </c>
+      <c r="F176" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="I176" t="n">
+        <v>91</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>14339.65</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3506</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="I177" t="n">
+        <v>88</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>14627.07</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3576.3</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="I178" t="n">
+        <v>91</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>12629.09</v>
+      </c>
+      <c r="E179" t="n">
+        <v>4526.6</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="I179" t="n">
+        <v>89</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>12225.18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>4381.8</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="I180" t="n">
+        <v>89</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>12059.44</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4322.4</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="I181" t="n">
+        <v>89</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>15837.7</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2517.9</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="I182" t="n">
+        <v>92</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>15526.04</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2468.4</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="I183" t="n">
+        <v>91</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>15395.01</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2447.5</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="I184" t="n">
+        <v>91</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>16515.88</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2544.8</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="I185" t="n">
+        <v>91</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>16155.21</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2489.2</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I186" t="n">
+        <v>92</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>15695.02</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2418.3</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="I187" t="n">
+        <v>89</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>17045.15</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3973.2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="I188" t="n">
+        <v>88</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>16308.59</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3801.5</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="I189" t="n">
+        <v>90</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>15907.34</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3708</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="I190" t="n">
+        <v>90</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>14615.43</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3573.5</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="I191" t="n">
+        <v>88</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>14181.86</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3467.4</v>
+      </c>
+      <c r="F192" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="I192" t="n">
+        <v>91</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>14315.82</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3500.2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="I193" t="n">
+        <v>88</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>12518.68</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4487</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="I194" t="n">
+        <v>92</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>11913.37</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4270</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="I195" t="n">
+        <v>89</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>12577.44</v>
+      </c>
+      <c r="E196" t="n">
+        <v>4508</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I196" t="n">
+        <v>88</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>15582.52</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2477.3</v>
+      </c>
+      <c r="F197" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I197" t="n">
+        <v>92</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>15752.39</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2504.4</v>
+      </c>
+      <c r="F198" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="I198" t="n">
+        <v>90</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>15795.71</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2511.2</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="I199" t="n">
+        <v>90</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>15462.4</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2382.5</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="I200" t="n">
+        <v>89</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>15779.22</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2431.3</v>
+      </c>
+      <c r="F201" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="I201" t="n">
+        <v>91</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>15668.17</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2414.2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="I202" t="n">
+        <v>91</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>16356.12</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3812.6</v>
+      </c>
+      <c r="F203" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="I203" t="n">
+        <v>92</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>16364.77</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3814.6</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="I204" t="n">
+        <v>92</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>16303.78</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3800.4</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="I205" t="n">
+        <v>90</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>14420.47</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3525.8</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="I206" t="n">
+        <v>91</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>14141.84</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3457.7</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="I207" t="n">
+        <v>91</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>14066.36</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3439.2</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="I208" t="n">
+        <v>89</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>11983.45</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4295.1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="I209" t="n">
+        <v>92</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>12528.05</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4490.3</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="I210" t="n">
+        <v>88</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>12758.01</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4572.8</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="I211" t="n">
+        <v>92</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>16787.69</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2668.9</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="I212" t="n">
+        <v>90</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>15897.93</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2527.5</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="I213" t="n">
+        <v>92</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>16638.01</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2645.2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="I214" t="n">
+        <v>89</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>15464.16</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2382.8</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="I215" t="n">
+        <v>92</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>16409.95</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2528.5</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="I216" t="n">
+        <v>90</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>16447.26</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2534.2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="I217" t="n">
+        <v>89</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>16651.82</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3881.5</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I218" t="n">
+        <v>90</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>16988.03</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3959.9</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="I219" t="n">
+        <v>90</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>15985.18</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3726.1</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="I220" t="n">
+        <v>89</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>14359.64</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3510.9</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="I221" t="n">
+        <v>90</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>14521.36</v>
+      </c>
+      <c r="E222" t="n">
+        <v>3550.5</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="I222" t="n">
+        <v>88</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>14086.54</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3444.1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="I223" t="n">
+        <v>89</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>12225.14</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4381.8</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="I224" t="n">
+        <v>90</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>12045.42</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4317.4</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.0856</v>
+      </c>
+      <c r="I225" t="n">
+        <v>90</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>12170.66</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4362.2</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="I226" t="n">
+        <v>92</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>45766</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CrestLine</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CL-Premium 12ct</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>13813.94</v>
-      </c>
-      <c r="E65" t="n">
-        <v>354.2</v>
-      </c>
-      <c r="F65" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.2543</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.2438</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>16960.85</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2696.5</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="I227" t="n">
+        <v>88</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>17947.57</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2853.3</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="I228" t="n">
+        <v>90</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>17691.5</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2812.6</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="I229" t="n">
+        <v>92</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>16663.62</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2567.6</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I230" t="n">
+        <v>88</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>16497.26</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2542</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="I231" t="n">
+        <v>90</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>15602.85</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2404.1</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="I232" t="n">
         <v>89</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>16551.46</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3858.1</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="I233" t="n">
+        <v>91</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>16080.44</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3748.4</v>
+      </c>
+      <c r="F234" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="I234" t="n">
+        <v>88</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>16936.98</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3948</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="I235" t="n">
+        <v>92</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>14720.2</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3599.1</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I236" t="n">
+        <v>92</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>14345.05</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3507.3</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="I237" t="n">
+        <v>88</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>15124.27</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3697.9</v>
+      </c>
+      <c r="F238" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="I238" t="n">
+        <v>89</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>11898.08</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4264.5</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I239" t="n">
+        <v>90</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>12338.72</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4422.5</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="I240" t="n">
+        <v>91</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>12493.08</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4477.8</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="I241" t="n">
+        <v>90</v>
+      </c>
+      <c r="J241" t="n">
         <v>0</v>
       </c>
     </row>

--- a/stella/test_fixtures/inventory_risk/iri_data.xlsx
+++ b/stella/test_fixtures/inventory_risk/iri_data.xlsx
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16648.35</v>
+        <v>3026.97</v>
       </c>
       <c r="E2" t="n">
-        <v>2646.8</v>
+        <v>481.2</v>
       </c>
       <c r="F2" t="n">
         <v>6.29</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17154.19</v>
+        <v>3118.94</v>
       </c>
       <c r="E3" t="n">
-        <v>2727.2</v>
+        <v>495.9</v>
       </c>
       <c r="F3" t="n">
         <v>6.29</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17913.5</v>
+        <v>3257</v>
       </c>
       <c r="E4" t="n">
-        <v>2847.9</v>
+        <v>517.8</v>
       </c>
       <c r="F4" t="n">
         <v>6.29</v>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15485.62</v>
+        <v>2815.57</v>
       </c>
       <c r="E5" t="n">
-        <v>2386.1</v>
+        <v>433.8</v>
       </c>
       <c r="F5" t="n">
         <v>6.49</v>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16383.63</v>
+        <v>2978.84</v>
       </c>
       <c r="E6" t="n">
-        <v>2524.4</v>
+        <v>459</v>
       </c>
       <c r="F6" t="n">
         <v>6.49</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15751.28</v>
+        <v>2863.87</v>
       </c>
       <c r="E7" t="n">
-        <v>2427</v>
+        <v>441.3</v>
       </c>
       <c r="F7" t="n">
         <v>6.49</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17000.91</v>
+        <v>3091.07</v>
       </c>
       <c r="E8" t="n">
-        <v>3962.9</v>
+        <v>720.5</v>
       </c>
       <c r="F8" t="n">
         <v>4.29</v>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16841.63</v>
+        <v>3062.12</v>
       </c>
       <c r="E9" t="n">
-        <v>3925.8</v>
+        <v>713.8</v>
       </c>
       <c r="F9" t="n">
         <v>4.29</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17026.14</v>
+        <v>3095.66</v>
       </c>
       <c r="E10" t="n">
-        <v>3968.8</v>
+        <v>721.6</v>
       </c>
       <c r="F10" t="n">
         <v>4.29</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14289.46</v>
+        <v>2598.08</v>
       </c>
       <c r="E11" t="n">
-        <v>3493.8</v>
+        <v>635.2</v>
       </c>
       <c r="F11" t="n">
         <v>4.09</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14658.35</v>
+        <v>2665.16</v>
       </c>
       <c r="E12" t="n">
-        <v>3583.9</v>
+        <v>651.6</v>
       </c>
       <c r="F12" t="n">
         <v>4.09</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14948.42</v>
+        <v>2717.9</v>
       </c>
       <c r="E13" t="n">
-        <v>3654.9</v>
+        <v>664.5</v>
       </c>
       <c r="F13" t="n">
         <v>4.09</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12026.26</v>
+        <v>2186.59</v>
       </c>
       <c r="E14" t="n">
-        <v>4310.5</v>
+        <v>783.7</v>
       </c>
       <c r="F14" t="n">
         <v>2.79</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12011.57</v>
+        <v>2183.92</v>
       </c>
       <c r="E15" t="n">
-        <v>4305.2</v>
+        <v>782.8</v>
       </c>
       <c r="F15" t="n">
         <v>2.79</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11811.66</v>
+        <v>2147.57</v>
       </c>
       <c r="E16" t="n">
-        <v>4233.6</v>
+        <v>769.7</v>
       </c>
       <c r="F16" t="n">
         <v>2.79</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17855.02</v>
+        <v>3246.37</v>
       </c>
       <c r="E17" t="n">
-        <v>2838.6</v>
+        <v>516.1</v>
       </c>
       <c r="F17" t="n">
         <v>6.29</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17881.32</v>
+        <v>3251.15</v>
       </c>
       <c r="E18" t="n">
-        <v>2842.8</v>
+        <v>516.9</v>
       </c>
       <c r="F18" t="n">
         <v>6.29</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17065.25</v>
+        <v>3102.77</v>
       </c>
       <c r="E19" t="n">
-        <v>2713.1</v>
+        <v>493.3</v>
       </c>
       <c r="F19" t="n">
         <v>6.29</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15637.58</v>
+        <v>2843.2</v>
       </c>
       <c r="E20" t="n">
-        <v>2409.5</v>
+        <v>438.1</v>
       </c>
       <c r="F20" t="n">
         <v>6.49</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15692.37</v>
+        <v>2853.16</v>
       </c>
       <c r="E21" t="n">
-        <v>2417.9</v>
+        <v>439.6</v>
       </c>
       <c r="F21" t="n">
         <v>6.49</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15535.89</v>
+        <v>2824.71</v>
       </c>
       <c r="E22" t="n">
-        <v>2393.8</v>
+        <v>435.2</v>
       </c>
       <c r="F22" t="n">
         <v>6.49</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16014.54</v>
+        <v>2911.74</v>
       </c>
       <c r="E23" t="n">
-        <v>3733</v>
+        <v>678.7</v>
       </c>
       <c r="F23" t="n">
         <v>4.29</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15950.06</v>
+        <v>2900.01</v>
       </c>
       <c r="E24" t="n">
-        <v>3718</v>
+        <v>676</v>
       </c>
       <c r="F24" t="n">
         <v>4.29</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17163.71</v>
+        <v>3120.68</v>
       </c>
       <c r="E25" t="n">
-        <v>4000.9</v>
+        <v>727.4</v>
       </c>
       <c r="F25" t="n">
         <v>4.29</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14123.51</v>
+        <v>2567.91</v>
       </c>
       <c r="E26" t="n">
-        <v>3453.2</v>
+        <v>627.9</v>
       </c>
       <c r="F26" t="n">
         <v>4.09</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14191.92</v>
+        <v>2580.35</v>
       </c>
       <c r="E27" t="n">
-        <v>3469.9</v>
+        <v>630.9</v>
       </c>
       <c r="F27" t="n">
         <v>4.09</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15004.55</v>
+        <v>2728.1</v>
       </c>
       <c r="E28" t="n">
-        <v>3668.6</v>
+        <v>667</v>
       </c>
       <c r="F28" t="n">
         <v>4.09</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12354.8</v>
+        <v>2246.33</v>
       </c>
       <c r="E29" t="n">
-        <v>4428.2</v>
+        <v>805.1</v>
       </c>
       <c r="F29" t="n">
         <v>2.79</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12545.5</v>
+        <v>2281</v>
       </c>
       <c r="E30" t="n">
-        <v>4496.6</v>
+        <v>817.6</v>
       </c>
       <c r="F30" t="n">
         <v>2.79</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12404.57</v>
+        <v>2255.38</v>
       </c>
       <c r="E31" t="n">
-        <v>4446.1</v>
+        <v>808.4</v>
       </c>
       <c r="F31" t="n">
         <v>2.79</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17790.7</v>
+        <v>3234.67</v>
       </c>
       <c r="E32" t="n">
-        <v>2828.4</v>
+        <v>514.3</v>
       </c>
       <c r="F32" t="n">
         <v>6.29</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16713.18</v>
+        <v>3038.76</v>
       </c>
       <c r="E33" t="n">
-        <v>2657.1</v>
+        <v>483.1</v>
       </c>
       <c r="F33" t="n">
         <v>6.29</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17664.24</v>
+        <v>3211.68</v>
       </c>
       <c r="E34" t="n">
-        <v>2808.3</v>
+        <v>510.6</v>
       </c>
       <c r="F34" t="n">
         <v>6.29</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15815.6</v>
+        <v>2875.56</v>
       </c>
       <c r="E35" t="n">
-        <v>2436.9</v>
+        <v>443.1</v>
       </c>
       <c r="F35" t="n">
         <v>6.49</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15698.6</v>
+        <v>2854.29</v>
       </c>
       <c r="E36" t="n">
-        <v>2418.9</v>
+        <v>439.8</v>
       </c>
       <c r="F36" t="n">
         <v>6.49</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16305.49</v>
+        <v>2964.63</v>
       </c>
       <c r="E37" t="n">
-        <v>2512.4</v>
+        <v>456.8</v>
       </c>
       <c r="F37" t="n">
         <v>6.49</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17057.97</v>
+        <v>3101.45</v>
       </c>
       <c r="E38" t="n">
-        <v>3976.2</v>
+        <v>722.9</v>
       </c>
       <c r="F38" t="n">
         <v>4.29</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16245.65</v>
+        <v>2953.76</v>
       </c>
       <c r="E39" t="n">
-        <v>3786.9</v>
+        <v>688.5</v>
       </c>
       <c r="F39" t="n">
         <v>4.29</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16607.45</v>
+        <v>3019.54</v>
       </c>
       <c r="E40" t="n">
-        <v>3871.2</v>
+        <v>703.9</v>
       </c>
       <c r="F40" t="n">
         <v>4.29</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14375.91</v>
+        <v>2613.8</v>
       </c>
       <c r="E41" t="n">
-        <v>3514.9</v>
+        <v>639.1</v>
       </c>
       <c r="F41" t="n">
         <v>4.09</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14685.25</v>
+        <v>2670.05</v>
       </c>
       <c r="E42" t="n">
-        <v>3590.5</v>
+        <v>652.8</v>
       </c>
       <c r="F42" t="n">
         <v>4.09</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14764.3</v>
+        <v>2684.42</v>
       </c>
       <c r="E43" t="n">
-        <v>3609.9</v>
+        <v>656.3</v>
       </c>
       <c r="F43" t="n">
         <v>4.09</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12384.36</v>
+        <v>2251.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4438.8</v>
+        <v>807.1</v>
       </c>
       <c r="F44" t="n">
         <v>2.79</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12397.33</v>
+        <v>2254.06</v>
       </c>
       <c r="E45" t="n">
-        <v>4443.5</v>
+        <v>807.9</v>
       </c>
       <c r="F45" t="n">
         <v>2.79</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11917.62</v>
+        <v>2166.84</v>
       </c>
       <c r="E46" t="n">
-        <v>4271.5</v>
+        <v>776.6</v>
       </c>
       <c r="F46" t="n">
         <v>2.79</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17296.38</v>
+        <v>3144.8</v>
       </c>
       <c r="E47" t="n">
-        <v>2749.8</v>
+        <v>500</v>
       </c>
       <c r="F47" t="n">
         <v>6.29</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17463.17</v>
+        <v>3175.12</v>
       </c>
       <c r="E48" t="n">
-        <v>2776.3</v>
+        <v>504.8</v>
       </c>
       <c r="F48" t="n">
         <v>6.29</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17889.73</v>
+        <v>3252.68</v>
       </c>
       <c r="E49" t="n">
-        <v>2844.2</v>
+        <v>517.1</v>
       </c>
       <c r="F49" t="n">
         <v>6.29</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16052.23</v>
+        <v>2918.59</v>
       </c>
       <c r="E50" t="n">
-        <v>2473.4</v>
+        <v>449.7</v>
       </c>
       <c r="F50" t="n">
         <v>6.49</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16099.58</v>
+        <v>2927.2</v>
       </c>
       <c r="E51" t="n">
-        <v>2480.7</v>
+        <v>451</v>
       </c>
       <c r="F51" t="n">
         <v>6.49</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16193.82</v>
+        <v>2944.33</v>
       </c>
       <c r="E52" t="n">
-        <v>2495.2</v>
+        <v>453.7</v>
       </c>
       <c r="F52" t="n">
         <v>6.49</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16830.33</v>
+        <v>3060.06</v>
       </c>
       <c r="E53" t="n">
-        <v>3923.2</v>
+        <v>713.3</v>
       </c>
       <c r="F53" t="n">
         <v>4.29</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15950.78</v>
+        <v>2900.14</v>
       </c>
       <c r="E54" t="n">
-        <v>3718.1</v>
+        <v>676</v>
       </c>
       <c r="F54" t="n">
         <v>4.29</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16537.23</v>
+        <v>3006.77</v>
       </c>
       <c r="E55" t="n">
-        <v>3854.8</v>
+        <v>700.9</v>
       </c>
       <c r="F55" t="n">
         <v>4.29</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14600.22</v>
+        <v>2654.58</v>
       </c>
       <c r="E56" t="n">
-        <v>3569.7</v>
+        <v>649</v>
       </c>
       <c r="F56" t="n">
         <v>4.09</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15115.01</v>
+        <v>2748.18</v>
       </c>
       <c r="E57" t="n">
-        <v>3695.6</v>
+        <v>671.9</v>
       </c>
       <c r="F57" t="n">
         <v>4.09</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14614.15</v>
+        <v>2657.12</v>
       </c>
       <c r="E58" t="n">
-        <v>3573.1</v>
+        <v>649.7</v>
       </c>
       <c r="F58" t="n">
         <v>4.09</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12244.89</v>
+        <v>2226.34</v>
       </c>
       <c r="E59" t="n">
-        <v>4388.8</v>
+        <v>798</v>
       </c>
       <c r="F59" t="n">
         <v>2.79</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12729.92</v>
+        <v>2314.53</v>
       </c>
       <c r="E60" t="n">
-        <v>4562.7</v>
+        <v>829.6</v>
       </c>
       <c r="F60" t="n">
         <v>2.79</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12227.46</v>
+        <v>2223.17</v>
       </c>
       <c r="E61" t="n">
-        <v>4382.6</v>
+        <v>796.8</v>
       </c>
       <c r="F61" t="n">
         <v>2.79</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>27525.42</v>
+        <v>5004.62</v>
       </c>
       <c r="E62" t="n">
-        <v>5461.4</v>
+        <v>993</v>
       </c>
       <c r="F62" t="n">
         <v>5.04</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28295.78</v>
+        <v>5144.69</v>
       </c>
       <c r="E63" t="n">
-        <v>5614.2</v>
+        <v>1020.8</v>
       </c>
       <c r="F63" t="n">
         <v>5.04</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>27122.75</v>
+        <v>4931.41</v>
       </c>
       <c r="E64" t="n">
-        <v>5381.5</v>
+        <v>978.5</v>
       </c>
       <c r="F64" t="n">
         <v>5.04</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14925.78</v>
+        <v>2713.78</v>
       </c>
       <c r="E65" t="n">
-        <v>2299.8</v>
+        <v>418.1</v>
       </c>
       <c r="F65" t="n">
         <v>6.49</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14456.72</v>
+        <v>2628.49</v>
       </c>
       <c r="E66" t="n">
-        <v>2227.5</v>
+        <v>405</v>
       </c>
       <c r="F66" t="n">
         <v>6.49</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14752.65</v>
+        <v>2682.3</v>
       </c>
       <c r="E67" t="n">
-        <v>2273.1</v>
+        <v>413.3</v>
       </c>
       <c r="F67" t="n">
         <v>6.49</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16299.46</v>
+        <v>2963.54</v>
       </c>
       <c r="E68" t="n">
-        <v>3799.4</v>
+        <v>690.8</v>
       </c>
       <c r="F68" t="n">
         <v>4.29</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16488.59</v>
+        <v>2997.93</v>
       </c>
       <c r="E69" t="n">
-        <v>3843.5</v>
+        <v>698.8</v>
       </c>
       <c r="F69" t="n">
         <v>4.29</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15505.67</v>
+        <v>2819.21</v>
       </c>
       <c r="E70" t="n">
-        <v>3614.4</v>
+        <v>657.2</v>
       </c>
       <c r="F70" t="n">
         <v>4.29</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13941.3</v>
+        <v>2534.78</v>
       </c>
       <c r="E71" t="n">
-        <v>3408.6</v>
+        <v>619.8</v>
       </c>
       <c r="F71" t="n">
         <v>4.09</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13899.93</v>
+        <v>2527.26</v>
       </c>
       <c r="E72" t="n">
-        <v>3398.5</v>
+        <v>617.9</v>
       </c>
       <c r="F72" t="n">
         <v>4.09</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13914.04</v>
+        <v>2529.83</v>
       </c>
       <c r="E73" t="n">
-        <v>3402</v>
+        <v>618.5</v>
       </c>
       <c r="F73" t="n">
         <v>4.09</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12233.4</v>
+        <v>2224.25</v>
       </c>
       <c r="E74" t="n">
-        <v>4384.7</v>
+        <v>797.2</v>
       </c>
       <c r="F74" t="n">
         <v>2.79</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12633.07</v>
+        <v>2296.92</v>
       </c>
       <c r="E75" t="n">
-        <v>4528</v>
+        <v>823.3</v>
       </c>
       <c r="F75" t="n">
         <v>2.79</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12629.92</v>
+        <v>2296.35</v>
       </c>
       <c r="E76" t="n">
-        <v>4526.9</v>
+        <v>823.1</v>
       </c>
       <c r="F76" t="n">
         <v>2.79</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27824.85</v>
+        <v>5059.06</v>
       </c>
       <c r="E77" t="n">
-        <v>5520.8</v>
+        <v>1003.8</v>
       </c>
       <c r="F77" t="n">
         <v>5.04</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>27854.78</v>
+        <v>5064.51</v>
       </c>
       <c r="E78" t="n">
-        <v>5526.7</v>
+        <v>1004.9</v>
       </c>
       <c r="F78" t="n">
         <v>5.04</v>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>27732.2</v>
+        <v>5042.22</v>
       </c>
       <c r="E79" t="n">
-        <v>5502.4</v>
+        <v>1000.4</v>
       </c>
       <c r="F79" t="n">
         <v>5.04</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14614.54</v>
+        <v>2657.19</v>
       </c>
       <c r="E80" t="n">
-        <v>2251.9</v>
+        <v>409.4</v>
       </c>
       <c r="F80" t="n">
         <v>6.49</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14350.45</v>
+        <v>2609.17</v>
       </c>
       <c r="E81" t="n">
-        <v>2211.2</v>
+        <v>402</v>
       </c>
       <c r="F81" t="n">
         <v>6.49</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14744.65</v>
+        <v>2680.85</v>
       </c>
       <c r="E82" t="n">
-        <v>2271.9</v>
+        <v>413.1</v>
       </c>
       <c r="F82" t="n">
         <v>6.49</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>15644.7</v>
+        <v>2844.49</v>
       </c>
       <c r="E83" t="n">
-        <v>3646.8</v>
+        <v>663.1</v>
       </c>
       <c r="F83" t="n">
         <v>4.29</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15641.06</v>
+        <v>2843.83</v>
       </c>
       <c r="E84" t="n">
-        <v>3645.9</v>
+        <v>662.9</v>
       </c>
       <c r="F84" t="n">
         <v>4.29</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>15382.99</v>
+        <v>2796.91</v>
       </c>
       <c r="E85" t="n">
-        <v>3585.8</v>
+        <v>652</v>
       </c>
       <c r="F85" t="n">
         <v>4.29</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13829.9</v>
+        <v>2514.53</v>
       </c>
       <c r="E86" t="n">
-        <v>3381.4</v>
+        <v>614.8</v>
       </c>
       <c r="F86" t="n">
         <v>4.09</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14580.82</v>
+        <v>2651.06</v>
       </c>
       <c r="E87" t="n">
-        <v>3565</v>
+        <v>648.2</v>
       </c>
       <c r="F87" t="n">
         <v>4.09</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14122.15</v>
+        <v>2567.66</v>
       </c>
       <c r="E88" t="n">
-        <v>3452.8</v>
+        <v>627.8</v>
       </c>
       <c r="F88" t="n">
         <v>4.09</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11888.66</v>
+        <v>2161.57</v>
       </c>
       <c r="E89" t="n">
-        <v>4261.2</v>
+        <v>774.8</v>
       </c>
       <c r="F89" t="n">
         <v>2.79</v>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12405.39</v>
+        <v>2255.52</v>
       </c>
       <c r="E90" t="n">
-        <v>4446.4</v>
+        <v>808.4</v>
       </c>
       <c r="F90" t="n">
         <v>2.79</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12205.72</v>
+        <v>2219.22</v>
       </c>
       <c r="E91" t="n">
-        <v>4374.8</v>
+        <v>795.4</v>
       </c>
       <c r="F91" t="n">
         <v>2.79</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28391.38</v>
+        <v>5162.07</v>
       </c>
       <c r="E92" t="n">
-        <v>5633.2</v>
+        <v>1024.2</v>
       </c>
       <c r="F92" t="n">
         <v>5.04</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>28591.63</v>
+        <v>5198.48</v>
       </c>
       <c r="E93" t="n">
-        <v>5672.9</v>
+        <v>1031.4</v>
       </c>
       <c r="F93" t="n">
         <v>5.04</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26635.63</v>
+        <v>4842.84</v>
       </c>
       <c r="E94" t="n">
-        <v>5284.8</v>
+        <v>960.9</v>
       </c>
       <c r="F94" t="n">
         <v>5.04</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14084.77</v>
+        <v>2560.87</v>
       </c>
       <c r="E95" t="n">
-        <v>2170.2</v>
+        <v>394.6</v>
       </c>
       <c r="F95" t="n">
         <v>6.49</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14923.6</v>
+        <v>2713.38</v>
       </c>
       <c r="E96" t="n">
-        <v>2299.5</v>
+        <v>418.1</v>
       </c>
       <c r="F96" t="n">
         <v>6.49</v>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14513.72</v>
+        <v>2638.86</v>
       </c>
       <c r="E97" t="n">
-        <v>2236.3</v>
+        <v>406.6</v>
       </c>
       <c r="F97" t="n">
         <v>6.49</v>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15411.93</v>
+        <v>2802.17</v>
       </c>
       <c r="E98" t="n">
-        <v>3592.5</v>
+        <v>653.2</v>
       </c>
       <c r="F98" t="n">
         <v>4.29</v>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>15478.84</v>
+        <v>2814.33</v>
       </c>
       <c r="E99" t="n">
-        <v>3608.1</v>
+        <v>656</v>
       </c>
       <c r="F99" t="n">
         <v>4.29</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>16058.78</v>
+        <v>2919.78</v>
       </c>
       <c r="E100" t="n">
-        <v>3743.3</v>
+        <v>680.6</v>
       </c>
       <c r="F100" t="n">
         <v>4.29</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>14438.19</v>
+        <v>2625.12</v>
       </c>
       <c r="E101" t="n">
-        <v>3530.1</v>
+        <v>641.8</v>
       </c>
       <c r="F101" t="n">
         <v>4.09</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14295.91</v>
+        <v>2599.26</v>
       </c>
       <c r="E102" t="n">
-        <v>3495.3</v>
+        <v>635.5</v>
       </c>
       <c r="F102" t="n">
         <v>4.09</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14697.26</v>
+        <v>2672.23</v>
       </c>
       <c r="E103" t="n">
-        <v>3593.5</v>
+        <v>653.4</v>
       </c>
       <c r="F103" t="n">
         <v>4.09</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12147.47</v>
+        <v>2208.63</v>
       </c>
       <c r="E104" t="n">
-        <v>4353.9</v>
+        <v>791.6</v>
       </c>
       <c r="F104" t="n">
         <v>2.79</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11959.05</v>
+        <v>2174.37</v>
       </c>
       <c r="E105" t="n">
-        <v>4286.4</v>
+        <v>779.3</v>
       </c>
       <c r="F105" t="n">
         <v>2.79</v>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12131.1</v>
+        <v>2205.66</v>
       </c>
       <c r="E106" t="n">
-        <v>4348.1</v>
+        <v>790.6</v>
       </c>
       <c r="F106" t="n">
         <v>2.79</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>27155.77</v>
+        <v>4937.41</v>
       </c>
       <c r="E107" t="n">
-        <v>5388</v>
+        <v>979.6</v>
       </c>
       <c r="F107" t="n">
         <v>5.04</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>26705.56</v>
+        <v>4855.56</v>
       </c>
       <c r="E108" t="n">
-        <v>5298.7</v>
+        <v>963.4</v>
       </c>
       <c r="F108" t="n">
         <v>5.04</v>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>27107.03</v>
+        <v>4928.55</v>
       </c>
       <c r="E109" t="n">
-        <v>5378.4</v>
+        <v>977.9</v>
       </c>
       <c r="F109" t="n">
         <v>5.04</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>14404.31</v>
+        <v>2618.97</v>
       </c>
       <c r="E110" t="n">
-        <v>2219.5</v>
+        <v>403.5</v>
       </c>
       <c r="F110" t="n">
         <v>6.49</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>14356.93</v>
+        <v>2610.35</v>
       </c>
       <c r="E111" t="n">
-        <v>2212.2</v>
+        <v>402.2</v>
       </c>
       <c r="F111" t="n">
         <v>6.49</v>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>14082.53</v>
+        <v>2560.46</v>
       </c>
       <c r="E112" t="n">
-        <v>2169.9</v>
+        <v>394.5</v>
       </c>
       <c r="F112" t="n">
         <v>6.49</v>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>16267.35</v>
+        <v>2957.7</v>
       </c>
       <c r="E113" t="n">
-        <v>3791.9</v>
+        <v>689.4</v>
       </c>
       <c r="F113" t="n">
         <v>4.29</v>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>16395.81</v>
+        <v>2981.06</v>
       </c>
       <c r="E114" t="n">
-        <v>3821.9</v>
+        <v>694.9</v>
       </c>
       <c r="F114" t="n">
         <v>4.29</v>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>15477.01</v>
+        <v>2814</v>
       </c>
       <c r="E115" t="n">
-        <v>3607.7</v>
+        <v>655.9</v>
       </c>
       <c r="F115" t="n">
         <v>4.29</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>14670.51</v>
+        <v>2667.37</v>
       </c>
       <c r="E116" t="n">
-        <v>3586.9</v>
+        <v>652.2</v>
       </c>
       <c r="F116" t="n">
         <v>4.09</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>13636.04</v>
+        <v>2479.28</v>
       </c>
       <c r="E117" t="n">
-        <v>3334</v>
+        <v>606.2</v>
       </c>
       <c r="F117" t="n">
         <v>4.09</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>14665.28</v>
+        <v>2666.41</v>
       </c>
       <c r="E118" t="n">
-        <v>3585.6</v>
+        <v>651.9</v>
       </c>
       <c r="F118" t="n">
         <v>4.09</v>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12592.63</v>
+        <v>2289.57</v>
       </c>
       <c r="E119" t="n">
-        <v>4513.5</v>
+        <v>820.6</v>
       </c>
       <c r="F119" t="n">
         <v>2.79</v>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11678.83</v>
+        <v>2123.42</v>
       </c>
       <c r="E120" t="n">
-        <v>4186</v>
+        <v>761.1</v>
       </c>
       <c r="F120" t="n">
         <v>2.79</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12408.96</v>
+        <v>2256.18</v>
       </c>
       <c r="E121" t="n">
-        <v>4447.7</v>
+        <v>808.7</v>
       </c>
       <c r="F121" t="n">
         <v>2.79</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>13807.52</v>
+        <v>2510.46</v>
       </c>
       <c r="E122" t="n">
-        <v>2195.2</v>
+        <v>399.1</v>
       </c>
       <c r="F122" t="n">
         <v>6.29</v>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>13848.88</v>
+        <v>2517.98</v>
       </c>
       <c r="E123" t="n">
-        <v>2201.7</v>
+        <v>400.3</v>
       </c>
       <c r="F123" t="n">
         <v>6.29</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>13630.11</v>
+        <v>2478.2</v>
       </c>
       <c r="E124" t="n">
-        <v>2166.9</v>
+        <v>394</v>
       </c>
       <c r="F124" t="n">
         <v>6.29</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>16666.01</v>
+        <v>3030.18</v>
       </c>
       <c r="E125" t="n">
-        <v>2568</v>
+        <v>466.9</v>
       </c>
       <c r="F125" t="n">
         <v>6.49</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>16362.32</v>
+        <v>2974.97</v>
       </c>
       <c r="E126" t="n">
-        <v>2521.2</v>
+        <v>458.4</v>
       </c>
       <c r="F126" t="n">
         <v>6.49</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>15894.4</v>
+        <v>2889.89</v>
       </c>
       <c r="E127" t="n">
-        <v>2449.1</v>
+        <v>445.3</v>
       </c>
       <c r="F127" t="n">
         <v>6.49</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16086.82</v>
+        <v>2924.88</v>
       </c>
       <c r="E128" t="n">
-        <v>3749.8</v>
+        <v>681.8</v>
       </c>
       <c r="F128" t="n">
         <v>4.29</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16145.97</v>
+        <v>2935.63</v>
       </c>
       <c r="E129" t="n">
-        <v>3763.6</v>
+        <v>684.3</v>
       </c>
       <c r="F129" t="n">
         <v>4.29</v>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16468.83</v>
+        <v>2994.33</v>
       </c>
       <c r="E130" t="n">
-        <v>3838.9</v>
+        <v>698</v>
       </c>
       <c r="F130" t="n">
         <v>4.29</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>15139.44</v>
+        <v>2752.63</v>
       </c>
       <c r="E131" t="n">
-        <v>3701.6</v>
+        <v>673</v>
       </c>
       <c r="F131" t="n">
         <v>4.09</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>14895.64</v>
+        <v>2708.3</v>
       </c>
       <c r="E132" t="n">
-        <v>3642</v>
+        <v>662.2</v>
       </c>
       <c r="F132" t="n">
         <v>4.09</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>14288.66</v>
+        <v>2597.94</v>
       </c>
       <c r="E133" t="n">
-        <v>3493.6</v>
+        <v>635.2</v>
       </c>
       <c r="F133" t="n">
         <v>4.09</v>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>12629.12</v>
+        <v>2296.2</v>
       </c>
       <c r="E134" t="n">
-        <v>4526.6</v>
+        <v>823</v>
       </c>
       <c r="F134" t="n">
         <v>2.79</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>12156.38</v>
+        <v>2210.25</v>
       </c>
       <c r="E135" t="n">
-        <v>4357.1</v>
+        <v>792.2</v>
       </c>
       <c r="F135" t="n">
         <v>2.79</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>12621.42</v>
+        <v>2294.8</v>
       </c>
       <c r="E136" t="n">
-        <v>4523.8</v>
+        <v>822.5</v>
       </c>
       <c r="F136" t="n">
         <v>2.79</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>14576.22</v>
+        <v>2650.22</v>
       </c>
       <c r="E137" t="n">
-        <v>2317.4</v>
+        <v>421.3</v>
       </c>
       <c r="F137" t="n">
         <v>6.29</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>14206.73</v>
+        <v>2583.04</v>
       </c>
       <c r="E138" t="n">
-        <v>2258.6</v>
+        <v>410.7</v>
       </c>
       <c r="F138" t="n">
         <v>6.29</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>14572.85</v>
+        <v>2649.61</v>
       </c>
       <c r="E139" t="n">
-        <v>2316.8</v>
+        <v>421.2</v>
       </c>
       <c r="F139" t="n">
         <v>6.29</v>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>15993.86</v>
+        <v>2907.97</v>
       </c>
       <c r="E140" t="n">
-        <v>2464.4</v>
+        <v>448.1</v>
       </c>
       <c r="F140" t="n">
         <v>6.49</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>16644.83</v>
+        <v>3026.33</v>
       </c>
       <c r="E141" t="n">
-        <v>2564.7</v>
+        <v>466.3</v>
       </c>
       <c r="F141" t="n">
         <v>6.49</v>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>16256.52</v>
+        <v>2955.73</v>
       </c>
       <c r="E142" t="n">
-        <v>2504.9</v>
+        <v>455.4</v>
       </c>
       <c r="F142" t="n">
         <v>6.49</v>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>16008.98</v>
+        <v>2910.72</v>
       </c>
       <c r="E143" t="n">
-        <v>3731.7</v>
+        <v>678.5</v>
       </c>
       <c r="F143" t="n">
         <v>4.29</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>17025.33</v>
+        <v>3095.51</v>
       </c>
       <c r="E144" t="n">
-        <v>3968.6</v>
+        <v>721.6</v>
       </c>
       <c r="F144" t="n">
         <v>4.29</v>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>16502.32</v>
+        <v>3000.42</v>
       </c>
       <c r="E145" t="n">
-        <v>3846.7</v>
+        <v>699.4</v>
       </c>
       <c r="F145" t="n">
         <v>4.29</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>14202.56</v>
+        <v>2582.28</v>
       </c>
       <c r="E146" t="n">
-        <v>3472.5</v>
+        <v>631.4</v>
       </c>
       <c r="F146" t="n">
         <v>4.09</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>14215.49</v>
+        <v>2584.63</v>
       </c>
       <c r="E147" t="n">
-        <v>3475.7</v>
+        <v>631.9</v>
       </c>
       <c r="F147" t="n">
         <v>4.09</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>14841.12</v>
+        <v>2698.38</v>
       </c>
       <c r="E148" t="n">
-        <v>3628.6</v>
+        <v>659.8</v>
       </c>
       <c r="F148" t="n">
         <v>4.09</v>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11831.48</v>
+        <v>2151.18</v>
       </c>
       <c r="E149" t="n">
-        <v>4240.7</v>
+        <v>771</v>
       </c>
       <c r="F149" t="n">
         <v>2.79</v>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12066.42</v>
+        <v>2193.89</v>
       </c>
       <c r="E150" t="n">
-        <v>4324.9</v>
+        <v>786.3</v>
       </c>
       <c r="F150" t="n">
         <v>2.79</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11922.24</v>
+        <v>2167.68</v>
       </c>
       <c r="E151" t="n">
-        <v>4273.2</v>
+        <v>776.9</v>
       </c>
       <c r="F151" t="n">
         <v>2.79</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>14565.28</v>
+        <v>2648.23</v>
       </c>
       <c r="E152" t="n">
-        <v>2315.6</v>
+        <v>421</v>
       </c>
       <c r="F152" t="n">
         <v>6.29</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>14638.6</v>
+        <v>2661.56</v>
       </c>
       <c r="E153" t="n">
-        <v>2327.3</v>
+        <v>423.1</v>
       </c>
       <c r="F153" t="n">
         <v>6.29</v>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>13974.08</v>
+        <v>2540.74</v>
       </c>
       <c r="E154" t="n">
-        <v>2221.6</v>
+        <v>403.9</v>
       </c>
       <c r="F154" t="n">
         <v>6.29</v>
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>16082.2</v>
+        <v>2924.04</v>
       </c>
       <c r="E155" t="n">
-        <v>2478</v>
+        <v>450.5</v>
       </c>
       <c r="F155" t="n">
         <v>6.49</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>15863.36</v>
+        <v>2884.25</v>
       </c>
       <c r="E156" t="n">
-        <v>2444.3</v>
+        <v>444.4</v>
       </c>
       <c r="F156" t="n">
         <v>6.49</v>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>15961.59</v>
+        <v>2902.11</v>
       </c>
       <c r="E157" t="n">
-        <v>2459.4</v>
+        <v>447.2</v>
       </c>
       <c r="F157" t="n">
         <v>6.49</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>15988.35</v>
+        <v>2906.97</v>
       </c>
       <c r="E158" t="n">
-        <v>3726.9</v>
+        <v>677.6</v>
       </c>
       <c r="F158" t="n">
         <v>4.29</v>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>16890.2</v>
+        <v>3070.94</v>
       </c>
       <c r="E159" t="n">
-        <v>3937.1</v>
+        <v>715.8</v>
       </c>
       <c r="F159" t="n">
         <v>4.29</v>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>17101.06</v>
+        <v>3109.28</v>
       </c>
       <c r="E160" t="n">
-        <v>3986.3</v>
+        <v>724.8</v>
       </c>
       <c r="F160" t="n">
         <v>4.29</v>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14062.93</v>
+        <v>2556.9</v>
       </c>
       <c r="E161" t="n">
-        <v>3438.4</v>
+        <v>625.2</v>
       </c>
       <c r="F161" t="n">
         <v>4.09</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14740.33</v>
+        <v>2680.06</v>
       </c>
       <c r="E162" t="n">
-        <v>3604</v>
+        <v>655.3</v>
       </c>
       <c r="F162" t="n">
         <v>4.09</v>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>14930.38</v>
+        <v>2714.61</v>
       </c>
       <c r="E163" t="n">
-        <v>3650.5</v>
+        <v>663.7</v>
       </c>
       <c r="F163" t="n">
         <v>4.09</v>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>12064.66</v>
+        <v>2193.58</v>
       </c>
       <c r="E164" t="n">
-        <v>4324.3</v>
+        <v>786.2</v>
       </c>
       <c r="F164" t="n">
         <v>2.79</v>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>12558.4</v>
+        <v>2283.35</v>
       </c>
       <c r="E165" t="n">
-        <v>4501.2</v>
+        <v>818.4</v>
       </c>
       <c r="F165" t="n">
         <v>2.79</v>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>12405.98</v>
+        <v>2255.63</v>
       </c>
       <c r="E166" t="n">
-        <v>4446.6</v>
+        <v>808.5</v>
       </c>
       <c r="F166" t="n">
         <v>2.79</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>14436.62</v>
+        <v>2624.84</v>
       </c>
       <c r="E167" t="n">
-        <v>2295.2</v>
+        <v>417.3</v>
       </c>
       <c r="F167" t="n">
         <v>6.29</v>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>14342.37</v>
+        <v>2607.7</v>
       </c>
       <c r="E168" t="n">
-        <v>2280.2</v>
+        <v>414.6</v>
       </c>
       <c r="F168" t="n">
         <v>6.29</v>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>15405.93</v>
+        <v>2801.08</v>
       </c>
       <c r="E169" t="n">
-        <v>2449.3</v>
+        <v>445.3</v>
       </c>
       <c r="F169" t="n">
         <v>6.29</v>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>15761.81</v>
+        <v>2865.78</v>
       </c>
       <c r="E170" t="n">
-        <v>2428.6</v>
+        <v>441.6</v>
       </c>
       <c r="F170" t="n">
         <v>6.49</v>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>16067.97</v>
+        <v>2921.45</v>
       </c>
       <c r="E171" t="n">
-        <v>2475.8</v>
+        <v>450.1</v>
       </c>
       <c r="F171" t="n">
         <v>6.49</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>15536.79</v>
+        <v>2824.87</v>
       </c>
       <c r="E172" t="n">
-        <v>2394</v>
+        <v>435.3</v>
       </c>
       <c r="F172" t="n">
         <v>6.49</v>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16415.62</v>
+        <v>2984.66</v>
       </c>
       <c r="E173" t="n">
-        <v>3826.5</v>
+        <v>695.7</v>
       </c>
       <c r="F173" t="n">
         <v>4.29</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>17084.81</v>
+        <v>3106.33</v>
       </c>
       <c r="E174" t="n">
-        <v>3982.5</v>
+        <v>724.1</v>
       </c>
       <c r="F174" t="n">
         <v>4.29</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>16519.69</v>
+        <v>3003.58</v>
       </c>
       <c r="E175" t="n">
-        <v>3850.7</v>
+        <v>700.1</v>
       </c>
       <c r="F175" t="n">
         <v>4.29</v>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>15172.86</v>
+        <v>2758.7</v>
       </c>
       <c r="E176" t="n">
-        <v>3709.7</v>
+        <v>674.5</v>
       </c>
       <c r="F176" t="n">
         <v>4.09</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>14339.65</v>
+        <v>2607.21</v>
       </c>
       <c r="E177" t="n">
-        <v>3506</v>
+        <v>637.5</v>
       </c>
       <c r="F177" t="n">
         <v>4.09</v>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>14627.07</v>
+        <v>2659.47</v>
       </c>
       <c r="E178" t="n">
-        <v>3576.3</v>
+        <v>650.2</v>
       </c>
       <c r="F178" t="n">
         <v>4.09</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>12629.09</v>
+        <v>2296.2</v>
       </c>
       <c r="E179" t="n">
-        <v>4526.6</v>
+        <v>823</v>
       </c>
       <c r="F179" t="n">
         <v>2.79</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>12225.18</v>
+        <v>2222.76</v>
       </c>
       <c r="E180" t="n">
-        <v>4381.8</v>
+        <v>796.7</v>
       </c>
       <c r="F180" t="n">
         <v>2.79</v>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>12059.44</v>
+        <v>2192.63</v>
       </c>
       <c r="E181" t="n">
-        <v>4322.4</v>
+        <v>785.9</v>
       </c>
       <c r="F181" t="n">
         <v>2.79</v>
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>15837.7</v>
+        <v>2879.58</v>
       </c>
       <c r="E182" t="n">
-        <v>2517.9</v>
+        <v>457.8</v>
       </c>
       <c r="F182" t="n">
         <v>6.29</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>15526.04</v>
+        <v>2822.92</v>
       </c>
       <c r="E183" t="n">
-        <v>2468.4</v>
+        <v>448.8</v>
       </c>
       <c r="F183" t="n">
         <v>6.29</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>15395.01</v>
+        <v>2799.09</v>
       </c>
       <c r="E184" t="n">
-        <v>2447.5</v>
+        <v>445</v>
       </c>
       <c r="F184" t="n">
         <v>6.29</v>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>16515.88</v>
+        <v>3002.89</v>
       </c>
       <c r="E185" t="n">
-        <v>2544.8</v>
+        <v>462.7</v>
       </c>
       <c r="F185" t="n">
         <v>6.49</v>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>16155.21</v>
+        <v>2937.31</v>
       </c>
       <c r="E186" t="n">
-        <v>2489.2</v>
+        <v>452.6</v>
       </c>
       <c r="F186" t="n">
         <v>6.49</v>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>15695.02</v>
+        <v>2853.64</v>
       </c>
       <c r="E187" t="n">
-        <v>2418.3</v>
+        <v>439.7</v>
       </c>
       <c r="F187" t="n">
         <v>6.49</v>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>17045.15</v>
+        <v>3099.12</v>
       </c>
       <c r="E188" t="n">
-        <v>3973.2</v>
+        <v>722.4</v>
       </c>
       <c r="F188" t="n">
         <v>4.29</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>16308.59</v>
+        <v>2965.2</v>
       </c>
       <c r="E189" t="n">
-        <v>3801.5</v>
+        <v>691.2</v>
       </c>
       <c r="F189" t="n">
         <v>4.29</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>15907.34</v>
+        <v>2892.24</v>
       </c>
       <c r="E190" t="n">
-        <v>3708</v>
+        <v>674.2</v>
       </c>
       <c r="F190" t="n">
         <v>4.29</v>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>14615.43</v>
+        <v>2657.35</v>
       </c>
       <c r="E191" t="n">
-        <v>3573.5</v>
+        <v>649.7</v>
       </c>
       <c r="F191" t="n">
         <v>4.09</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>14181.86</v>
+        <v>2578.52</v>
       </c>
       <c r="E192" t="n">
-        <v>3467.4</v>
+        <v>630.4</v>
       </c>
       <c r="F192" t="n">
         <v>4.09</v>
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>14315.82</v>
+        <v>2602.88</v>
       </c>
       <c r="E193" t="n">
-        <v>3500.2</v>
+        <v>636.4</v>
       </c>
       <c r="F193" t="n">
         <v>4.09</v>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>12518.68</v>
+        <v>2276.12</v>
       </c>
       <c r="E194" t="n">
-        <v>4487</v>
+        <v>815.8</v>
       </c>
       <c r="F194" t="n">
         <v>2.79</v>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>11913.37</v>
+        <v>2166.07</v>
       </c>
       <c r="E195" t="n">
-        <v>4270</v>
+        <v>776.4</v>
       </c>
       <c r="F195" t="n">
         <v>2.79</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>12577.44</v>
+        <v>2286.81</v>
       </c>
       <c r="E196" t="n">
-        <v>4508</v>
+        <v>819.6</v>
       </c>
       <c r="F196" t="n">
         <v>2.79</v>
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>15582.52</v>
+        <v>2833.19</v>
       </c>
       <c r="E197" t="n">
-        <v>2477.3</v>
+        <v>450.4</v>
       </c>
       <c r="F197" t="n">
         <v>6.29</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>15752.39</v>
+        <v>2864.07</v>
       </c>
       <c r="E198" t="n">
-        <v>2504.4</v>
+        <v>455.3</v>
       </c>
       <c r="F198" t="n">
         <v>6.29</v>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>15795.71</v>
+        <v>2871.95</v>
       </c>
       <c r="E199" t="n">
-        <v>2511.2</v>
+        <v>456.6</v>
       </c>
       <c r="F199" t="n">
         <v>6.29</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>15462.4</v>
+        <v>2811.35</v>
       </c>
       <c r="E200" t="n">
-        <v>2382.5</v>
+        <v>433.2</v>
       </c>
       <c r="F200" t="n">
         <v>6.49</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>15779.22</v>
+        <v>2868.95</v>
       </c>
       <c r="E201" t="n">
-        <v>2431.3</v>
+        <v>442.1</v>
       </c>
       <c r="F201" t="n">
         <v>6.49</v>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>15668.17</v>
+        <v>2848.76</v>
       </c>
       <c r="E202" t="n">
-        <v>2414.2</v>
+        <v>438.9</v>
       </c>
       <c r="F202" t="n">
         <v>6.49</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>16356.12</v>
+        <v>2973.84</v>
       </c>
       <c r="E203" t="n">
-        <v>3812.6</v>
+        <v>693.2</v>
       </c>
       <c r="F203" t="n">
         <v>4.29</v>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>16364.77</v>
+        <v>2975.41</v>
       </c>
       <c r="E204" t="n">
-        <v>3814.6</v>
+        <v>693.6</v>
       </c>
       <c r="F204" t="n">
         <v>4.29</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>16303.78</v>
+        <v>2964.32</v>
       </c>
       <c r="E205" t="n">
-        <v>3800.4</v>
+        <v>691</v>
       </c>
       <c r="F205" t="n">
         <v>4.29</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>14420.47</v>
+        <v>2621.9</v>
       </c>
       <c r="E206" t="n">
-        <v>3525.8</v>
+        <v>641.1</v>
       </c>
       <c r="F206" t="n">
         <v>4.09</v>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>14141.84</v>
+        <v>2571.24</v>
       </c>
       <c r="E207" t="n">
-        <v>3457.7</v>
+        <v>628.7</v>
       </c>
       <c r="F207" t="n">
         <v>4.09</v>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>14066.36</v>
+        <v>2557.52</v>
       </c>
       <c r="E208" t="n">
-        <v>3439.2</v>
+        <v>625.3</v>
       </c>
       <c r="F208" t="n">
         <v>4.09</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>11983.45</v>
+        <v>2178.81</v>
       </c>
       <c r="E209" t="n">
-        <v>4295.1</v>
+        <v>780.9</v>
       </c>
       <c r="F209" t="n">
         <v>2.79</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>12528.05</v>
+        <v>2277.83</v>
       </c>
       <c r="E210" t="n">
-        <v>4490.3</v>
+        <v>816.4</v>
       </c>
       <c r="F210" t="n">
         <v>2.79</v>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>12758.01</v>
+        <v>2319.64</v>
       </c>
       <c r="E211" t="n">
-        <v>4572.8</v>
+        <v>831.4</v>
       </c>
       <c r="F211" t="n">
         <v>2.79</v>
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>16787.69</v>
+        <v>3052.31</v>
       </c>
       <c r="E212" t="n">
-        <v>2668.9</v>
+        <v>485.3</v>
       </c>
       <c r="F212" t="n">
         <v>6.29</v>
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>15897.93</v>
+        <v>2890.53</v>
       </c>
       <c r="E213" t="n">
-        <v>2527.5</v>
+        <v>459.5</v>
       </c>
       <c r="F213" t="n">
         <v>6.29</v>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>16638.01</v>
+        <v>3025.09</v>
       </c>
       <c r="E214" t="n">
-        <v>2645.2</v>
+        <v>480.9</v>
       </c>
       <c r="F214" t="n">
         <v>6.29</v>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>15464.16</v>
+        <v>2811.67</v>
       </c>
       <c r="E215" t="n">
-        <v>2382.8</v>
+        <v>433.2</v>
       </c>
       <c r="F215" t="n">
         <v>6.49</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>16409.95</v>
+        <v>2983.63</v>
       </c>
       <c r="E216" t="n">
-        <v>2528.5</v>
+        <v>459.7</v>
       </c>
       <c r="F216" t="n">
         <v>6.49</v>
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>16447.26</v>
+        <v>2990.41</v>
       </c>
       <c r="E217" t="n">
-        <v>2534.2</v>
+        <v>460.8</v>
       </c>
       <c r="F217" t="n">
         <v>6.49</v>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>16651.82</v>
+        <v>3027.6</v>
       </c>
       <c r="E218" t="n">
-        <v>3881.5</v>
+        <v>705.7</v>
       </c>
       <c r="F218" t="n">
         <v>4.29</v>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>16988.03</v>
+        <v>3088.73</v>
       </c>
       <c r="E219" t="n">
-        <v>3959.9</v>
+        <v>720</v>
       </c>
       <c r="F219" t="n">
         <v>4.29</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>15985.18</v>
+        <v>2906.4</v>
       </c>
       <c r="E220" t="n">
-        <v>3726.1</v>
+        <v>677.5</v>
       </c>
       <c r="F220" t="n">
         <v>4.29</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>14359.64</v>
+        <v>2610.84</v>
       </c>
       <c r="E221" t="n">
-        <v>3510.9</v>
+        <v>638.3</v>
       </c>
       <c r="F221" t="n">
         <v>4.09</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>14521.36</v>
+        <v>2640.25</v>
       </c>
       <c r="E222" t="n">
-        <v>3550.5</v>
+        <v>645.5</v>
       </c>
       <c r="F222" t="n">
         <v>4.09</v>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>14086.54</v>
+        <v>2561.19</v>
       </c>
       <c r="E223" t="n">
-        <v>3444.1</v>
+        <v>626.2</v>
       </c>
       <c r="F223" t="n">
         <v>4.09</v>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>12225.14</v>
+        <v>2222.75</v>
       </c>
       <c r="E224" t="n">
-        <v>4381.8</v>
+        <v>796.7</v>
       </c>
       <c r="F224" t="n">
         <v>2.79</v>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>12045.42</v>
+        <v>2190.08</v>
       </c>
       <c r="E225" t="n">
-        <v>4317.4</v>
+        <v>785</v>
       </c>
       <c r="F225" t="n">
         <v>2.79</v>
@@ -8563,10 +8563,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>12170.66</v>
+        <v>2212.85</v>
       </c>
       <c r="E226" t="n">
-        <v>4362.2</v>
+        <v>793.1</v>
       </c>
       <c r="F226" t="n">
         <v>2.79</v>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>16960.85</v>
+        <v>3083.79</v>
       </c>
       <c r="E227" t="n">
-        <v>2696.5</v>
+        <v>490.3</v>
       </c>
       <c r="F227" t="n">
         <v>6.29</v>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>17947.57</v>
+        <v>3263.19</v>
       </c>
       <c r="E228" t="n">
-        <v>2853.3</v>
+        <v>518.8</v>
       </c>
       <c r="F228" t="n">
         <v>6.29</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>17691.5</v>
+        <v>3216.64</v>
       </c>
       <c r="E229" t="n">
-        <v>2812.6</v>
+        <v>511.4</v>
       </c>
       <c r="F229" t="n">
         <v>6.29</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>16663.62</v>
+        <v>3029.75</v>
       </c>
       <c r="E230" t="n">
-        <v>2567.6</v>
+        <v>466.8</v>
       </c>
       <c r="F230" t="n">
         <v>6.49</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>16497.26</v>
+        <v>2999.5</v>
       </c>
       <c r="E231" t="n">
-        <v>2542</v>
+        <v>462.2</v>
       </c>
       <c r="F231" t="n">
         <v>6.49</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>15602.85</v>
+        <v>2836.88</v>
       </c>
       <c r="E232" t="n">
-        <v>2404.1</v>
+        <v>437.1</v>
       </c>
       <c r="F232" t="n">
         <v>6.49</v>
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>16551.46</v>
+        <v>3009.36</v>
       </c>
       <c r="E233" t="n">
-        <v>3858.1</v>
+        <v>701.5</v>
       </c>
       <c r="F233" t="n">
         <v>4.29</v>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>16080.44</v>
+        <v>2923.72</v>
       </c>
       <c r="E234" t="n">
-        <v>3748.4</v>
+        <v>681.5</v>
       </c>
       <c r="F234" t="n">
         <v>4.29</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>16936.98</v>
+        <v>3079.45</v>
       </c>
       <c r="E235" t="n">
-        <v>3948</v>
+        <v>717.8</v>
       </c>
       <c r="F235" t="n">
         <v>4.29</v>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>14720.2</v>
+        <v>2676.4</v>
       </c>
       <c r="E236" t="n">
-        <v>3599.1</v>
+        <v>654.4</v>
       </c>
       <c r="F236" t="n">
         <v>4.09</v>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>14345.05</v>
+        <v>2608.19</v>
       </c>
       <c r="E237" t="n">
-        <v>3507.3</v>
+        <v>637.7</v>
       </c>
       <c r="F237" t="n">
         <v>4.09</v>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>15124.27</v>
+        <v>2749.87</v>
       </c>
       <c r="E238" t="n">
-        <v>3697.9</v>
+        <v>672.3</v>
       </c>
       <c r="F238" t="n">
         <v>4.09</v>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11898.08</v>
+        <v>2163.29</v>
       </c>
       <c r="E239" t="n">
-        <v>4264.5</v>
+        <v>775.4</v>
       </c>
       <c r="F239" t="n">
         <v>2.79</v>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>12338.72</v>
+        <v>2243.4</v>
       </c>
       <c r="E240" t="n">
-        <v>4422.5</v>
+        <v>804.1</v>
       </c>
       <c r="F240" t="n">
         <v>2.79</v>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12493.08</v>
+        <v>2271.47</v>
       </c>
       <c r="E241" t="n">
-        <v>4477.8</v>
+        <v>814.1</v>
       </c>
       <c r="F241" t="n">
         <v>2.79</v>

--- a/stella/test_fixtures/inventory_risk/iri_data.xlsx
+++ b/stella/test_fixtures/inventory_risk/iri_data.xlsx
@@ -508,10 +508,10 @@
         <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0519</v>
+        <v>0.0534</v>
       </c>
       <c r="I2" t="n">
         <v>92</v>
@@ -544,10 +544,10 @@
         <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0746</v>
+        <v>0.075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0535</v>
+        <v>0.0537</v>
       </c>
       <c r="I3" t="n">
         <v>91</v>
@@ -580,10 +580,10 @@
         <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0779</v>
+        <v>0.0756</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0558</v>
+        <v>0.0541</v>
       </c>
       <c r="I4" t="n">
         <v>91</v>
@@ -616,10 +616,10 @@
         <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0673</v>
+        <v>0.0693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0468</v>
+        <v>0.0481</v>
       </c>
       <c r="I5" t="n">
         <v>91</v>
@@ -652,10 +652,10 @@
         <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0712</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0495</v>
+        <v>0.0486</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -688,10 +688,10 @@
         <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0476</v>
+        <v>0.0482</v>
       </c>
       <c r="I7" t="n">
         <v>90</v>
@@ -724,10 +724,10 @@
         <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0721</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="I8" t="n">
         <v>90</v>
@@ -760,10 +760,10 @@
         <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0732</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.077</v>
+        <v>0.0756</v>
       </c>
       <c r="I9" t="n">
         <v>91</v>
@@ -796,10 +796,10 @@
         <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.074</v>
+        <v>0.0721</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0757</v>
       </c>
       <c r="I10" t="n">
         <v>89</v>
@@ -832,10 +832,10 @@
         <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0621</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="I11" t="n">
         <v>92</v>
@@ -868,10 +868,10 @@
         <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0703</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>91</v>
@@ -904,10 +904,10 @@
         <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.065</v>
+        <v>0.0638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0717</v>
+        <v>0.0702</v>
       </c>
       <c r="I13" t="n">
         <v>89</v>
@@ -940,10 +940,10 @@
         <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0523</v>
+        <v>0.0531</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="I14" t="n">
         <v>90</v>
@@ -976,10 +976,10 @@
         <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0522</v>
+        <v>0.0531</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0844</v>
+        <v>0.0857</v>
       </c>
       <c r="I15" t="n">
         <v>88</v>
@@ -1012,10 +1012,10 @@
         <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0514</v>
+        <v>0.0529</v>
       </c>
       <c r="H16" t="n">
-        <v>0.083</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>92</v>
@@ -1048,10 +1048,10 @@
         <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0756</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0556</v>
+        <v>0.0541</v>
       </c>
       <c r="I17" t="n">
         <v>92</v>
@@ -1084,10 +1084,10 @@
         <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0779</v>
+        <v>0.0756</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0557</v>
+        <v>0.0541</v>
       </c>
       <c r="I18" t="n">
         <v>91</v>
@@ -1120,10 +1120,10 @@
         <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0532</v>
+        <v>0.0537</v>
       </c>
       <c r="I19" t="n">
         <v>90</v>
@@ -1156,10 +1156,10 @@
         <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0682</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0472</v>
+        <v>0.0482</v>
       </c>
       <c r="I20" t="n">
         <v>91</v>
@@ -1192,10 +1192,10 @@
         <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0684</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0474</v>
+        <v>0.0482</v>
       </c>
       <c r="I21" t="n">
         <v>90</v>
@@ -1228,10 +1228,10 @@
         <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0677</v>
+        <v>0.0694</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0469</v>
+        <v>0.0481</v>
       </c>
       <c r="I22" t="n">
         <v>89</v>
@@ -1264,10 +1264,10 @@
         <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0698</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0732</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>90</v>
@@ -1300,10 +1300,10 @@
         <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>88</v>
@@ -1336,10 +1336,10 @@
         <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0723</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0784</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>91</v>
@@ -1372,10 +1372,10 @@
         <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0616</v>
+        <v>0.0631</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0677</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>89</v>
@@ -1408,10 +1408,10 @@
         <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0619</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.068</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>88</v>
@@ -1444,10 +1444,10 @@
         <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0654</v>
+        <v>0.0638</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="I28" t="n">
         <v>89</v>
@@ -1480,10 +1480,10 @@
         <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0539</v>
+        <v>0.0534</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0868</v>
+        <v>0.0862</v>
       </c>
       <c r="I29" t="n">
         <v>92</v>
@@ -1516,10 +1516,10 @@
         <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0547</v>
+        <v>0.0535</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0881</v>
+        <v>0.0864</v>
       </c>
       <c r="I30" t="n">
         <v>89</v>
@@ -1552,10 +1552,10 @@
         <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0541</v>
+        <v>0.0534</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="I31" t="n">
         <v>91</v>
@@ -1588,10 +1588,10 @@
         <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0772</v>
+        <v>0.0755</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0553</v>
+        <v>0.054</v>
       </c>
       <c r="I32" t="n">
         <v>91</v>
@@ -1624,10 +1624,10 @@
         <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0725</v>
+        <v>0.0746</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0519</v>
+        <v>0.0534</v>
       </c>
       <c r="I33" t="n">
         <v>91</v>
@@ -1660,10 +1660,10 @@
         <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0767</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0549</v>
+        <v>0.054</v>
       </c>
       <c r="I34" t="n">
         <v>91</v>
@@ -1696,10 +1696,10 @@
         <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0476</v>
+        <v>0.0482</v>
       </c>
       <c r="I35" t="n">
         <v>88</v>
@@ -1732,10 +1732,10 @@
         <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0473</v>
+        <v>0.0482</v>
       </c>
       <c r="I36" t="n">
         <v>90</v>
@@ -1768,10 +1768,10 @@
         <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0708</v>
+        <v>0.0699</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1804,10 +1804,10 @@
         <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.074</v>
+        <v>0.0721</v>
       </c>
       <c r="H38" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="I38" t="n">
         <v>88</v>
@@ -1840,10 +1840,10 @@
         <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="I39" t="n">
         <v>89</v>
@@ -1876,10 +1876,10 @@
         <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0721</v>
+        <v>0.0718</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0757</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>90</v>
@@ -1912,10 +1912,10 @@
         <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0624</v>
+        <v>0.0633</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0687</v>
+        <v>0.0697</v>
       </c>
       <c r="I41" t="n">
         <v>91</v>
@@ -1948,10 +1948,10 @@
         <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0702</v>
+        <v>0.0699</v>
       </c>
       <c r="I42" t="n">
         <v>89</v>
@@ -1984,10 +1984,10 @@
         <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0641</v>
+        <v>0.0636</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0706</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>92</v>
@@ -2020,10 +2020,10 @@
         <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0537</v>
+        <v>0.0534</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0868</v>
+        <v>0.0862</v>
       </c>
       <c r="I44" t="n">
         <v>90</v>
@@ -2056,10 +2056,10 @@
         <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0538</v>
+        <v>0.0534</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0868</v>
+        <v>0.0862</v>
       </c>
       <c r="I45" t="n">
         <v>91</v>
@@ -2092,10 +2092,10 @@
         <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0517</v>
+        <v>0.053</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0835</v>
+        <v>0.0856</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2128,10 +2128,10 @@
         <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0746</v>
+        <v>0.075</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0534</v>
+        <v>0.0537</v>
       </c>
       <c r="I47" t="n">
         <v>88</v>
@@ -2164,10 +2164,10 @@
         <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0539</v>
+        <v>0.0538</v>
       </c>
       <c r="I48" t="n">
         <v>89</v>
@@ -2200,10 +2200,10 @@
         <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0772</v>
+        <v>0.0755</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0552</v>
+        <v>0.054</v>
       </c>
       <c r="I49" t="n">
         <v>88</v>
@@ -2236,10 +2236,10 @@
         <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0692</v>
+        <v>0.0696</v>
       </c>
       <c r="H50" t="n">
-        <v>0.048</v>
+        <v>0.0483</v>
       </c>
       <c r="I50" t="n">
         <v>88</v>
@@ -2272,10 +2272,10 @@
         <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0694</v>
+        <v>0.0697</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0482</v>
+        <v>0.0483</v>
       </c>
       <c r="I51" t="n">
         <v>90</v>
@@ -2311,7 +2311,7 @@
         <v>0.0698</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0485</v>
+        <v>0.0484</v>
       </c>
       <c r="I52" t="n">
         <v>91</v>
@@ -2344,10 +2344,10 @@
         <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0726</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0762</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>91</v>
@@ -2380,10 +2380,10 @@
         <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0688</v>
+        <v>0.0712</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0722</v>
+        <v>0.0747</v>
       </c>
       <c r="I54" t="n">
         <v>88</v>
@@ -2416,10 +2416,10 @@
         <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0713</v>
+        <v>0.0716</v>
       </c>
       <c r="H55" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0752</v>
       </c>
       <c r="I55" t="n">
         <v>90</v>
@@ -2452,10 +2452,10 @@
         <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.063</v>
+        <v>0.0634</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0693</v>
+        <v>0.0698</v>
       </c>
       <c r="I56" t="n">
         <v>88</v>
@@ -2488,10 +2488,10 @@
         <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0638</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0718</v>
+        <v>0.0702</v>
       </c>
       <c r="I57" t="n">
         <v>92</v>
@@ -2524,10 +2524,10 @@
         <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.063</v>
+        <v>0.0634</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0694</v>
+        <v>0.0698</v>
       </c>
       <c r="I58" t="n">
         <v>88</v>
@@ -2560,10 +2560,10 @@
         <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0528</v>
+        <v>0.0532</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0852</v>
+        <v>0.0859</v>
       </c>
       <c r="I59" t="n">
         <v>91</v>
@@ -2596,10 +2596,10 @@
         <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0549</v>
+        <v>0.0536</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0886</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I60" t="n">
         <v>89</v>
@@ -2632,10 +2632,10 @@
         <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0527</v>
+        <v>0.0532</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0851</v>
+        <v>0.0859</v>
       </c>
       <c r="I61" t="n">
         <v>91</v>
@@ -2668,10 +2668,10 @@
         <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1081</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0939</v>
+        <v>0.0619</v>
       </c>
       <c r="I62" t="n">
         <v>90</v>
@@ -2704,10 +2704,10 @@
         <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1111</v>
+        <v>0.0822</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0965</v>
+        <v>0.0624</v>
       </c>
       <c r="I63" t="n">
         <v>91</v>
@@ -2740,10 +2740,10 @@
         <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1065</v>
+        <v>0.0813</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0925</v>
+        <v>0.0616</v>
       </c>
       <c r="I64" t="n">
         <v>92</v>
@@ -2776,10 +2776,10 @@
         <v>6.49</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0395</v>
+        <v>0.0466</v>
       </c>
       <c r="I65" t="n">
         <v>92</v>
@@ -2812,10 +2812,10 @@
         <v>6.49</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0568</v>
+        <v>0.0672</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0383</v>
+        <v>0.0464</v>
       </c>
       <c r="I66" t="n">
         <v>89</v>
@@ -2848,10 +2848,10 @@
         <v>6.49</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0579</v>
+        <v>0.0674</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0391</v>
+        <v>0.0465</v>
       </c>
       <c r="I67" t="n">
         <v>90</v>
@@ -2884,10 +2884,10 @@
         <v>4.29</v>
       </c>
       <c r="G68" t="n">
-        <v>0.064</v>
+        <v>0.0702</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0653</v>
+        <v>0.0733</v>
       </c>
       <c r="I68" t="n">
         <v>92</v>
@@ -2920,10 +2920,10 @@
         <v>4.29</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0648</v>
+        <v>0.0703</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>89</v>
@@ -2956,10 +2956,10 @@
         <v>4.29</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0609</v>
+        <v>0.0696</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0621</v>
+        <v>0.0726</v>
       </c>
       <c r="I70" t="n">
         <v>90</v>
@@ -2992,10 +2992,10 @@
         <v>4.09</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0548</v>
+        <v>0.0618</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0586</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>92</v>
@@ -3028,10 +3028,10 @@
         <v>4.09</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0546</v>
+        <v>0.0617</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0584</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>92</v>
@@ -3064,10 +3064,10 @@
         <v>4.09</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0546</v>
+        <v>0.0617</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0585</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I73" t="n">
         <v>92</v>
@@ -3100,10 +3100,10 @@
         <v>2.79</v>
       </c>
       <c r="G74" t="n">
-        <v>0.048</v>
+        <v>0.0523</v>
       </c>
       <c r="H74" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0839</v>
       </c>
       <c r="I74" t="n">
         <v>91</v>
@@ -3136,10 +3136,10 @@
         <v>2.79</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0496</v>
+        <v>0.0526</v>
       </c>
       <c r="H75" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0844</v>
       </c>
       <c r="I75" t="n">
         <v>89</v>
@@ -3172,10 +3172,10 @@
         <v>2.79</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0496</v>
+        <v>0.0526</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0844</v>
       </c>
       <c r="I76" t="n">
         <v>89</v>
@@ -3208,10 +3208,10 @@
         <v>5.04</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1101</v>
+        <v>0.082</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0958</v>
+        <v>0.0622</v>
       </c>
       <c r="I77" t="n">
         <v>87</v>
@@ -3244,10 +3244,10 @@
         <v>5.04</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1102</v>
+        <v>0.082</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0959</v>
+        <v>0.0622</v>
       </c>
       <c r="I78" t="n">
         <v>89</v>
@@ -3280,10 +3280,10 @@
         <v>5.04</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1097</v>
+        <v>0.0819</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0955</v>
+        <v>0.0621</v>
       </c>
       <c r="I79" t="n">
         <v>88</v>
@@ -3316,10 +3316,10 @@
         <v>6.49</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0578</v>
+        <v>0.0674</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0391</v>
+        <v>0.0465</v>
       </c>
       <c r="I80" t="n">
         <v>91</v>
@@ -3352,10 +3352,10 @@
         <v>6.49</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0568</v>
+        <v>0.0672</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0384</v>
+        <v>0.0464</v>
       </c>
       <c r="I81" t="n">
         <v>89</v>
@@ -3388,10 +3388,10 @@
         <v>6.49</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0583</v>
+        <v>0.0675</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0394</v>
+        <v>0.0466</v>
       </c>
       <c r="I82" t="n">
         <v>88</v>
@@ -3424,10 +3424,10 @@
         <v>4.29</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0619</v>
+        <v>0.0698</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0633</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>88</v>
@@ -3460,10 +3460,10 @@
         <v>4.29</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0619</v>
+        <v>0.0698</v>
       </c>
       <c r="H84" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>90</v>
@@ -3496,10 +3496,10 @@
         <v>4.29</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0608</v>
+        <v>0.0696</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0622</v>
+        <v>0.0727</v>
       </c>
       <c r="I85" t="n">
         <v>88</v>
@@ -3532,10 +3532,10 @@
         <v>4.09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0547</v>
+        <v>0.0618</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0587</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I86" t="n">
         <v>92</v>
@@ -3568,10 +3568,10 @@
         <v>4.09</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0577</v>
+        <v>0.0623</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0618</v>
+        <v>0.0683</v>
       </c>
       <c r="I87" t="n">
         <v>88</v>
@@ -3604,10 +3604,10 @@
         <v>4.09</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0559</v>
+        <v>0.062</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0599</v>
+        <v>0.0679</v>
       </c>
       <c r="I88" t="n">
         <v>91</v>
@@ -3640,10 +3640,10 @@
         <v>2.79</v>
       </c>
       <c r="G89" t="n">
-        <v>0.047</v>
+        <v>0.0521</v>
       </c>
       <c r="H89" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="I89" t="n">
         <v>90</v>
@@ -3676,10 +3676,10 @@
         <v>2.79</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0491</v>
+        <v>0.0525</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0771</v>
+        <v>0.0842</v>
       </c>
       <c r="I90" t="n">
         <v>90</v>
@@ -3712,10 +3712,10 @@
         <v>2.79</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0483</v>
+        <v>0.0523</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0759</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I91" t="n">
         <v>88</v>
@@ -3748,10 +3748,10 @@
         <v>5.04</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1119</v>
+        <v>0.0823</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0974</v>
+        <v>0.0625</v>
       </c>
       <c r="I92" t="n">
         <v>89</v>
@@ -3784,10 +3784,10 @@
         <v>5.04</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1127</v>
+        <v>0.0825</v>
       </c>
       <c r="H93" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="I93" t="n">
         <v>88</v>
@@ -3820,10 +3820,10 @@
         <v>5.04</v>
       </c>
       <c r="G94" t="n">
-        <v>0.105</v>
+        <v>0.081</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0914</v>
+        <v>0.0613</v>
       </c>
       <c r="I94" t="n">
         <v>87</v>
@@ -3856,10 +3856,10 @@
         <v>6.49</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0555</v>
+        <v>0.0669</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0375</v>
+        <v>0.0462</v>
       </c>
       <c r="I95" t="n">
         <v>89</v>
@@ -3892,10 +3892,10 @@
         <v>6.49</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0588</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0398</v>
+        <v>0.0467</v>
       </c>
       <c r="I96" t="n">
         <v>91</v>
@@ -3928,10 +3928,10 @@
         <v>6.49</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0572</v>
+        <v>0.0673</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0387</v>
+        <v>0.0464</v>
       </c>
       <c r="I97" t="n">
         <v>88</v>
@@ -3964,10 +3964,10 @@
         <v>4.29</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0607</v>
+        <v>0.0696</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0621</v>
+        <v>0.0726</v>
       </c>
       <c r="I98" t="n">
         <v>90</v>
@@ -4000,10 +4000,10 @@
         <v>4.29</v>
       </c>
       <c r="G99" t="n">
-        <v>0.061</v>
+        <v>0.0696</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0624</v>
+        <v>0.0727</v>
       </c>
       <c r="I99" t="n">
         <v>91</v>
@@ -4036,10 +4036,10 @@
         <v>4.29</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0633</v>
+        <v>0.0701</v>
       </c>
       <c r="H100" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="I100" t="n">
         <v>91</v>
@@ -4072,10 +4072,10 @@
         <v>4.09</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0569</v>
+        <v>0.0622</v>
       </c>
       <c r="H101" t="n">
-        <v>0.061</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="I101" t="n">
         <v>91</v>
@@ -4108,10 +4108,10 @@
         <v>4.09</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0563</v>
+        <v>0.0621</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0604</v>
+        <v>0.068</v>
       </c>
       <c r="I102" t="n">
         <v>91</v>
@@ -4144,10 +4144,10 @@
         <v>4.09</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0579</v>
+        <v>0.0624</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0621</v>
+        <v>0.0683</v>
       </c>
       <c r="I103" t="n">
         <v>91</v>
@@ -4180,10 +4180,10 @@
         <v>2.79</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0479</v>
+        <v>0.0522</v>
       </c>
       <c r="H104" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0839</v>
       </c>
       <c r="I104" t="n">
         <v>88</v>
@@ -4216,10 +4216,10 @@
         <v>2.79</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0471</v>
+        <v>0.0521</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0741</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="I105" t="n">
         <v>90</v>
@@ -4252,10 +4252,10 @@
         <v>2.79</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0478</v>
+        <v>0.0522</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0752</v>
+        <v>0.0838</v>
       </c>
       <c r="I106" t="n">
         <v>90</v>
@@ -4288,10 +4288,10 @@
         <v>5.04</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1079</v>
+        <v>0.0815</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0936</v>
+        <v>0.0617</v>
       </c>
       <c r="I107" t="n">
         <v>93</v>
@@ -4324,10 +4324,10 @@
         <v>5.04</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1061</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0921</v>
+        <v>0.0614</v>
       </c>
       <c r="I108" t="n">
         <v>93</v>
@@ -4360,10 +4360,10 @@
         <v>5.04</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1077</v>
+        <v>0.0815</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0935</v>
+        <v>0.0617</v>
       </c>
       <c r="I109" t="n">
         <v>93</v>
@@ -4396,10 +4396,10 @@
         <v>6.49</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0572</v>
+        <v>0.0673</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0386</v>
+        <v>0.0464</v>
       </c>
       <c r="I110" t="n">
         <v>90</v>
@@ -4432,10 +4432,10 @@
         <v>6.49</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0571</v>
+        <v>0.0673</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0384</v>
+        <v>0.0464</v>
       </c>
       <c r="I111" t="n">
         <v>88</v>
@@ -4468,10 +4468,10 @@
         <v>6.49</v>
       </c>
       <c r="G112" t="n">
-        <v>0.056</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0377</v>
+        <v>0.0463</v>
       </c>
       <c r="I112" t="n">
         <v>92</v>
@@ -4504,10 +4504,10 @@
         <v>4.29</v>
       </c>
       <c r="G113" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0703</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0659</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I113" t="n">
         <v>91</v>
@@ -4540,10 +4540,10 @@
         <v>4.29</v>
       </c>
       <c r="G114" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0704</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0664</v>
+        <v>0.0735</v>
       </c>
       <c r="I114" t="n">
         <v>91</v>
@@ -4576,10 +4576,10 @@
         <v>4.29</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0615</v>
+        <v>0.0697</v>
       </c>
       <c r="H115" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0728</v>
       </c>
       <c r="I115" t="n">
         <v>90</v>
@@ -4612,10 +4612,10 @@
         <v>4.09</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0583</v>
+        <v>0.0625</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0623</v>
+        <v>0.0684</v>
       </c>
       <c r="I116" t="n">
         <v>90</v>
@@ -4648,10 +4648,10 @@
         <v>4.09</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0542</v>
+        <v>0.0617</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0579</v>
+        <v>0.0675</v>
       </c>
       <c r="I117" t="n">
         <v>88</v>
@@ -4684,10 +4684,10 @@
         <v>4.09</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0583</v>
+        <v>0.0625</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0623</v>
+        <v>0.0684</v>
       </c>
       <c r="I118" t="n">
         <v>91</v>
@@ -4720,10 +4720,10 @@
         <v>2.79</v>
       </c>
       <c r="G119" t="n">
-        <v>0.05</v>
+        <v>0.0527</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0784</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I119" t="n">
         <v>88</v>
@@ -4756,10 +4756,10 @@
         <v>2.79</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0464</v>
+        <v>0.052</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0727</v>
+        <v>0.0834</v>
       </c>
       <c r="I120" t="n">
         <v>91</v>
@@ -4792,10 +4792,10 @@
         <v>2.79</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0493</v>
+        <v>0.0525</v>
       </c>
       <c r="H121" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="I121" t="n">
         <v>92</v>
@@ -4828,10 +4828,10 @@
         <v>6.29</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0626</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0442</v>
+        <v>0.0521</v>
       </c>
       <c r="I122" t="n">
         <v>89</v>
@@ -4864,10 +4864,10 @@
         <v>6.29</v>
       </c>
       <c r="G123" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0443</v>
+        <v>0.0521</v>
       </c>
       <c r="I123" t="n">
         <v>91</v>
@@ -4900,10 +4900,10 @@
         <v>6.29</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0618</v>
+        <v>0.0728</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0436</v>
+        <v>0.052</v>
       </c>
       <c r="I124" t="n">
         <v>92</v>
@@ -4936,10 +4936,10 @@
         <v>6.49</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0755</v>
+        <v>0.0708</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0517</v>
+        <v>0.049</v>
       </c>
       <c r="I125" t="n">
         <v>89</v>
@@ -4972,10 +4972,10 @@
         <v>6.49</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0742</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0507</v>
+        <v>0.0488</v>
       </c>
       <c r="I126" t="n">
         <v>91</v>
@@ -5008,10 +5008,10 @@
         <v>6.49</v>
       </c>
       <c r="G127" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0493</v>
+        <v>0.0485</v>
       </c>
       <c r="I127" t="n">
         <v>92</v>
@@ -5044,10 +5044,10 @@
         <v>4.29</v>
       </c>
       <c r="G128" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0755</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I128" t="n">
         <v>88</v>
@@ -5080,10 +5080,10 @@
         <v>4.29</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0732</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0757</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I129" t="n">
         <v>88</v>
@@ -5116,10 +5116,10 @@
         <v>4.29</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0746</v>
+        <v>0.0722</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0772</v>
+        <v>0.0756</v>
       </c>
       <c r="I130" t="n">
         <v>91</v>
@@ -5152,10 +5152,10 @@
         <v>4.09</v>
       </c>
       <c r="G131" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0644</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0745</v>
+        <v>0.0707</v>
       </c>
       <c r="I131" t="n">
         <v>89</v>
@@ -5188,10 +5188,10 @@
         <v>4.09</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0675</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0733</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I132" t="n">
         <v>88</v>
@@ -5224,10 +5224,10 @@
         <v>4.09</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0648</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0703</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I133" t="n">
         <v>90</v>
@@ -5260,10 +5260,10 @@
         <v>2.79</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0572</v>
+        <v>0.054</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0911</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I134" t="n">
         <v>91</v>
@@ -5296,10 +5296,10 @@
         <v>2.79</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0551</v>
+        <v>0.0536</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0877</v>
+        <v>0.0863</v>
       </c>
       <c r="I135" t="n">
         <v>89</v>
@@ -5332,10 +5332,10 @@
         <v>2.79</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0572</v>
+        <v>0.054</v>
       </c>
       <c r="H136" t="n">
-        <v>0.091</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I136" t="n">
         <v>89</v>
@@ -5368,10 +5368,10 @@
         <v>6.29</v>
       </c>
       <c r="G137" t="n">
-        <v>0.066</v>
+        <v>0.0735</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0469</v>
+        <v>0.0526</v>
       </c>
       <c r="I137" t="n">
         <v>90</v>
@@ -5404,10 +5404,10 @@
         <v>6.29</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0643</v>
+        <v>0.0732</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0457</v>
+        <v>0.0523</v>
       </c>
       <c r="I138" t="n">
         <v>90</v>
@@ -5440,10 +5440,10 @@
         <v>6.29</v>
       </c>
       <c r="G139" t="n">
-        <v>0.066</v>
+        <v>0.0735</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0469</v>
+        <v>0.0526</v>
       </c>
       <c r="I139" t="n">
         <v>90</v>
@@ -5476,10 +5476,10 @@
         <v>6.49</v>
       </c>
       <c r="G140" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0499</v>
+        <v>0.0487</v>
       </c>
       <c r="I140" t="n">
         <v>89</v>
@@ -5512,10 +5512,10 @@
         <v>6.49</v>
       </c>
       <c r="G141" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0519</v>
+        <v>0.049</v>
       </c>
       <c r="I141" t="n">
         <v>88</v>
@@ -5548,10 +5548,10 @@
         <v>6.49</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0736</v>
+        <v>0.0704</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0507</v>
+        <v>0.0488</v>
       </c>
       <c r="I142" t="n">
         <v>91</v>
@@ -5584,10 +5584,10 @@
         <v>4.29</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0725</v>
+        <v>0.0718</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0756</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I143" t="n">
         <v>89</v>
@@ -5620,10 +5620,10 @@
         <v>4.29</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0771</v>
+        <v>0.0727</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0804</v>
+        <v>0.0762</v>
       </c>
       <c r="I144" t="n">
         <v>91</v>
@@ -5656,10 +5656,10 @@
         <v>4.29</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0747</v>
+        <v>0.0722</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0779</v>
+        <v>0.0757</v>
       </c>
       <c r="I145" t="n">
         <v>88</v>
@@ -5692,10 +5692,10 @@
         <v>4.09</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0643</v>
+        <v>0.0636</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0703</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I146" t="n">
         <v>88</v>
@@ -5728,10 +5728,10 @@
         <v>4.09</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0644</v>
+        <v>0.0636</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0704</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I147" t="n">
         <v>89</v>
@@ -5764,10 +5764,10 @@
         <v>4.09</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0672</v>
+        <v>0.0641</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0735</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I148" t="n">
         <v>90</v>
@@ -5800,10 +5800,10 @@
         <v>2.79</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0536</v>
+        <v>0.0533</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0859</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I149" t="n">
         <v>89</v>
@@ -5836,10 +5836,10 @@
         <v>2.79</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0546</v>
+        <v>0.0535</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0876</v>
+        <v>0.0863</v>
       </c>
       <c r="I150" t="n">
         <v>91</v>
@@ -5872,10 +5872,10 @@
         <v>2.79</v>
       </c>
       <c r="G151" t="n">
-        <v>0.054</v>
+        <v>0.0534</v>
       </c>
       <c r="H151" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="I151" t="n">
         <v>89</v>
@@ -5908,10 +5908,10 @@
         <v>6.29</v>
       </c>
       <c r="G152" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0464</v>
+        <v>0.0525</v>
       </c>
       <c r="I152" t="n">
         <v>92</v>
@@ -5944,10 +5944,10 @@
         <v>6.29</v>
       </c>
       <c r="G153" t="n">
-        <v>0.066</v>
+        <v>0.0735</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0467</v>
+        <v>0.0525</v>
       </c>
       <c r="I153" t="n">
         <v>92</v>
@@ -5980,10 +5980,10 @@
         <v>6.29</v>
       </c>
       <c r="G154" t="n">
-        <v>0.063</v>
+        <v>0.073</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0446</v>
+        <v>0.0521</v>
       </c>
       <c r="I154" t="n">
         <v>88</v>
@@ -6016,10 +6016,10 @@
         <v>6.49</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0725</v>
+        <v>0.0702</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0497</v>
+        <v>0.0486</v>
       </c>
       <c r="I155" t="n">
         <v>90</v>
@@ -6052,10 +6052,10 @@
         <v>6.49</v>
       </c>
       <c r="G156" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="H156" t="n">
-        <v>0.049</v>
+        <v>0.0485</v>
       </c>
       <c r="I156" t="n">
         <v>90</v>
@@ -6088,10 +6088,10 @@
         <v>6.49</v>
       </c>
       <c r="G157" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0493</v>
+        <v>0.0486</v>
       </c>
       <c r="I157" t="n">
         <v>88</v>
@@ -6124,10 +6124,10 @@
         <v>4.29</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0721</v>
+        <v>0.0718</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0747</v>
+        <v>0.0752</v>
       </c>
       <c r="I158" t="n">
         <v>89</v>
@@ -6160,10 +6160,10 @@
         <v>4.29</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0761</v>
+        <v>0.0725</v>
       </c>
       <c r="H159" t="n">
-        <v>0.079</v>
+        <v>0.0759</v>
       </c>
       <c r="I159" t="n">
         <v>92</v>
@@ -6196,10 +6196,10 @@
         <v>4.29</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0771</v>
+        <v>0.0727</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0799</v>
+        <v>0.0761</v>
       </c>
       <c r="I160" t="n">
         <v>88</v>
@@ -6232,10 +6232,10 @@
         <v>4.09</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0634</v>
+        <v>0.0635</v>
       </c>
       <c r="H161" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I161" t="n">
         <v>90</v>
@@ -6268,10 +6268,10 @@
         <v>4.09</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0664</v>
+        <v>0.064</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0723</v>
+        <v>0.0703</v>
       </c>
       <c r="I162" t="n">
         <v>92</v>
@@ -6304,10 +6304,10 @@
         <v>4.09</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0673</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0732</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I163" t="n">
         <v>89</v>
@@ -6340,10 +6340,10 @@
         <v>2.79</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0544</v>
+        <v>0.0535</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0867</v>
+        <v>0.0861</v>
       </c>
       <c r="I164" t="n">
         <v>90</v>
@@ -6376,10 +6376,10 @@
         <v>2.79</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0566</v>
+        <v>0.0539</v>
       </c>
       <c r="H165" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="I165" t="n">
         <v>92</v>
@@ -6412,10 +6412,10 @@
         <v>2.79</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0559</v>
+        <v>0.0538</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0892</v>
+        <v>0.0866</v>
       </c>
       <c r="I166" t="n">
         <v>90</v>
@@ -6448,10 +6448,10 @@
         <v>6.29</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0648</v>
+        <v>0.0733</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0459</v>
+        <v>0.0524</v>
       </c>
       <c r="I167" t="n">
         <v>92</v>
@@ -6484,10 +6484,10 @@
         <v>6.29</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0644</v>
+        <v>0.0732</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0456</v>
+        <v>0.0523</v>
       </c>
       <c r="I168" t="n">
         <v>89</v>
@@ -6520,10 +6520,10 @@
         <v>6.29</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0692</v>
+        <v>0.0741</v>
       </c>
       <c r="H169" t="n">
-        <v>0.049</v>
+        <v>0.0529</v>
       </c>
       <c r="I169" t="n">
         <v>90</v>
@@ -6556,10 +6556,10 @@
         <v>6.49</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0708</v>
+        <v>0.0699</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0486</v>
+        <v>0.0484</v>
       </c>
       <c r="I170" t="n">
         <v>92</v>
@@ -6592,10 +6592,10 @@
         <v>6.49</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0722</v>
+        <v>0.0702</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0495</v>
+        <v>0.0486</v>
       </c>
       <c r="I171" t="n">
         <v>88</v>
@@ -6628,10 +6628,10 @@
         <v>6.49</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0698</v>
+        <v>0.0697</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0479</v>
+        <v>0.0483</v>
       </c>
       <c r="I172" t="n">
         <v>89</v>
@@ -6664,10 +6664,10 @@
         <v>4.29</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0737</v>
+        <v>0.0721</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0765</v>
+        <v>0.0755</v>
       </c>
       <c r="I173" t="n">
         <v>88</v>
@@ -6700,10 +6700,10 @@
         <v>4.29</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0767</v>
+        <v>0.0726</v>
       </c>
       <c r="H174" t="n">
-        <v>0.0796</v>
+        <v>0.076</v>
       </c>
       <c r="I174" t="n">
         <v>89</v>
@@ -6736,10 +6736,10 @@
         <v>4.29</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0742</v>
+        <v>0.0722</v>
       </c>
       <c r="H175" t="n">
-        <v>0.077</v>
+        <v>0.0756</v>
       </c>
       <c r="I175" t="n">
         <v>89</v>
@@ -6772,10 +6772,10 @@
         <v>4.09</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0682</v>
+        <v>0.0643</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0742</v>
+        <v>0.0707</v>
       </c>
       <c r="I176" t="n">
         <v>91</v>
@@ -6808,10 +6808,10 @@
         <v>4.09</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0644</v>
+        <v>0.0636</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0701</v>
+        <v>0.0699</v>
       </c>
       <c r="I177" t="n">
         <v>88</v>
@@ -6844,10 +6844,10 @@
         <v>4.09</v>
       </c>
       <c r="G178" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0639</v>
       </c>
       <c r="H178" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="I178" t="n">
         <v>91</v>
@@ -6880,10 +6880,10 @@
         <v>2.79</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0567</v>
+        <v>0.0539</v>
       </c>
       <c r="H179" t="n">
-        <v>0.0905</v>
+        <v>0.0868</v>
       </c>
       <c r="I179" t="n">
         <v>89</v>
@@ -6916,10 +6916,10 @@
         <v>2.79</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0549</v>
+        <v>0.0536</v>
       </c>
       <c r="H180" t="n">
-        <v>0.0876</v>
+        <v>0.0863</v>
       </c>
       <c r="I180" t="n">
         <v>89</v>
@@ -6952,10 +6952,10 @@
         <v>2.79</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0864</v>
+        <v>0.0861</v>
       </c>
       <c r="I181" t="n">
         <v>89</v>
@@ -6988,10 +6988,10 @@
         <v>6.29</v>
       </c>
       <c r="G182" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0762</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0502</v>
+        <v>0.0546</v>
       </c>
       <c r="I182" t="n">
         <v>92</v>
@@ -7024,10 +7024,10 @@
         <v>6.29</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0692</v>
+        <v>0.0759</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0492</v>
+        <v>0.0544</v>
       </c>
       <c r="I183" t="n">
         <v>91</v>
@@ -7060,10 +7060,10 @@
         <v>6.29</v>
       </c>
       <c r="G184" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0488</v>
+        <v>0.0543</v>
       </c>
       <c r="I184" t="n">
         <v>91</v>
@@ -7096,10 +7096,10 @@
         <v>6.49</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0736</v>
+        <v>0.0699</v>
       </c>
       <c r="H185" t="n">
-        <v>0.0507</v>
+        <v>0.0485</v>
       </c>
       <c r="I185" t="n">
         <v>91</v>
@@ -7132,10 +7132,10 @@
         <v>6.49</v>
       </c>
       <c r="G186" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0696</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0496</v>
+        <v>0.0484</v>
       </c>
       <c r="I186" t="n">
         <v>92</v>
@@ -7168,10 +7168,10 @@
         <v>6.49</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0699</v>
+        <v>0.0693</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0482</v>
+        <v>0.0481</v>
       </c>
       <c r="I187" t="n">
         <v>89</v>
@@ -7204,10 +7204,10 @@
         <v>4.29</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0759</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H188" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="I188" t="n">
         <v>88</v>
@@ -7240,10 +7240,10 @@
         <v>4.29</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0726</v>
+        <v>0.0713</v>
       </c>
       <c r="H189" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I189" t="n">
         <v>90</v>
@@ -7276,10 +7276,10 @@
         <v>4.29</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0709</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H190" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="I190" t="n">
         <v>90</v>
@@ -7312,10 +7312,10 @@
         <v>4.09</v>
       </c>
       <c r="G191" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="H191" t="n">
-        <v>0.0712</v>
+        <v>0.0698</v>
       </c>
       <c r="I191" t="n">
         <v>88</v>
@@ -7348,10 +7348,10 @@
         <v>4.09</v>
       </c>
       <c r="G192" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="H192" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="I192" t="n">
         <v>91</v>
@@ -7384,10 +7384,10 @@
         <v>4.09</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0638</v>
+        <v>0.0631</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0698</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I193" t="n">
         <v>88</v>
@@ -7420,10 +7420,10 @@
         <v>2.79</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0558</v>
+        <v>0.0533</v>
       </c>
       <c r="H194" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="I194" t="n">
         <v>92</v>
@@ -7456,10 +7456,10 @@
         <v>2.79</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0531</v>
+        <v>0.0529</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0851</v>
+        <v>0.0854</v>
       </c>
       <c r="I195" t="n">
         <v>89</v>
@@ -7492,10 +7492,10 @@
         <v>2.79</v>
       </c>
       <c r="G196" t="n">
-        <v>0.056</v>
+        <v>0.0534</v>
       </c>
       <c r="H196" t="n">
-        <v>0.0898</v>
+        <v>0.0862</v>
       </c>
       <c r="I196" t="n">
         <v>88</v>
@@ -7528,10 +7528,10 @@
         <v>6.29</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0699</v>
+        <v>0.0761</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0496</v>
+        <v>0.0545</v>
       </c>
       <c r="I197" t="n">
         <v>92</v>
@@ -7564,10 +7564,10 @@
         <v>6.29</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0707</v>
+        <v>0.0762</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0502</v>
+        <v>0.0546</v>
       </c>
       <c r="I198" t="n">
         <v>90</v>
@@ -7600,10 +7600,10 @@
         <v>6.29</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0708</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H199" t="n">
-        <v>0.0503</v>
+        <v>0.0546</v>
       </c>
       <c r="I199" t="n">
         <v>90</v>
@@ -7636,10 +7636,10 @@
         <v>6.49</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0693</v>
+        <v>0.0692</v>
       </c>
       <c r="H200" t="n">
-        <v>0.0477</v>
+        <v>0.048</v>
       </c>
       <c r="I200" t="n">
         <v>89</v>
@@ -7672,10 +7672,10 @@
         <v>6.49</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0708</v>
+        <v>0.0694</v>
       </c>
       <c r="H201" t="n">
-        <v>0.0487</v>
+        <v>0.0482</v>
       </c>
       <c r="I201" t="n">
         <v>91</v>
@@ -7708,10 +7708,10 @@
         <v>6.49</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0703</v>
+        <v>0.0693</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0484</v>
+        <v>0.0481</v>
       </c>
       <c r="I202" t="n">
         <v>91</v>
@@ -7744,10 +7744,10 @@
         <v>4.29</v>
       </c>
       <c r="G203" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H203" t="n">
-        <v>0.0764</v>
+        <v>0.0751</v>
       </c>
       <c r="I203" t="n">
         <v>92</v>
@@ -7780,10 +7780,10 @@
         <v>4.29</v>
       </c>
       <c r="G204" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0764</v>
+        <v>0.0751</v>
       </c>
       <c r="I204" t="n">
         <v>92</v>
@@ -7816,10 +7816,10 @@
         <v>4.29</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0731</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0761</v>
+        <v>0.075</v>
       </c>
       <c r="I205" t="n">
         <v>90</v>
@@ -7852,10 +7852,10 @@
         <v>4.09</v>
       </c>
       <c r="G206" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0706</v>
+        <v>0.0697</v>
       </c>
       <c r="I206" t="n">
         <v>91</v>
@@ -7888,10 +7888,10 @@
         <v>4.09</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0634</v>
+        <v>0.063</v>
       </c>
       <c r="H207" t="n">
-        <v>0.0693</v>
+        <v>0.0694</v>
       </c>
       <c r="I207" t="n">
         <v>91</v>
@@ -7924,10 +7924,10 @@
         <v>4.09</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0631</v>
+        <v>0.0629</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0689</v>
+        <v>0.0693</v>
       </c>
       <c r="I208" t="n">
         <v>89</v>
@@ -7960,10 +7960,10 @@
         <v>2.79</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0537</v>
+        <v>0.053</v>
       </c>
       <c r="H209" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0856</v>
       </c>
       <c r="I209" t="n">
         <v>92</v>
@@ -7996,10 +7996,10 @@
         <v>2.79</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0562</v>
+        <v>0.0534</v>
       </c>
       <c r="H210" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="I210" t="n">
         <v>88</v>
@@ -8032,10 +8032,10 @@
         <v>2.79</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0572</v>
+        <v>0.0536</v>
       </c>
       <c r="H211" t="n">
-        <v>0.0916</v>
+        <v>0.0866</v>
       </c>
       <c r="I211" t="n">
         <v>92</v>
@@ -8068,10 +8068,10 @@
         <v>6.29</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0741</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="H212" t="n">
-        <v>0.0529</v>
+        <v>0.0551</v>
       </c>
       <c r="I212" t="n">
         <v>90</v>
@@ -8104,10 +8104,10 @@
         <v>6.29</v>
       </c>
       <c r="G213" t="n">
-        <v>0.0701</v>
+        <v>0.0761</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0501</v>
+        <v>0.0546</v>
       </c>
       <c r="I213" t="n">
         <v>92</v>
@@ -8140,10 +8140,10 @@
         <v>6.29</v>
       </c>
       <c r="G214" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="H214" t="n">
-        <v>0.0525</v>
+        <v>0.055</v>
       </c>
       <c r="I214" t="n">
         <v>89</v>
@@ -8176,10 +8176,10 @@
         <v>6.49</v>
       </c>
       <c r="G215" t="n">
-        <v>0.0682</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0473</v>
+        <v>0.0479</v>
       </c>
       <c r="I215" t="n">
         <v>92</v>
@@ -8212,10 +8212,10 @@
         <v>6.49</v>
       </c>
       <c r="G216" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0501</v>
+        <v>0.0484</v>
       </c>
       <c r="I216" t="n">
         <v>90</v>
@@ -8248,10 +8248,10 @@
         <v>6.49</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0726</v>
+        <v>0.0697</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0503</v>
+        <v>0.0485</v>
       </c>
       <c r="I217" t="n">
         <v>89</v>
@@ -8284,10 +8284,10 @@
         <v>4.29</v>
       </c>
       <c r="G218" t="n">
-        <v>0.0735</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H218" t="n">
-        <v>0.077</v>
+        <v>0.0752</v>
       </c>
       <c r="I218" t="n">
         <v>90</v>
@@ -8320,10 +8320,10 @@
         <v>4.29</v>
       </c>
       <c r="G219" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0785</v>
+        <v>0.0755</v>
       </c>
       <c r="I219" t="n">
         <v>90</v>
@@ -8356,10 +8356,10 @@
         <v>4.29</v>
       </c>
       <c r="G220" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H220" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="I220" t="n">
         <v>89</v>
@@ -8392,10 +8392,10 @@
         <v>4.09</v>
       </c>
       <c r="G221" t="n">
-        <v>0.0633</v>
+        <v>0.063</v>
       </c>
       <c r="H221" t="n">
-        <v>0.0696</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I221" t="n">
         <v>90</v>
@@ -8428,10 +8428,10 @@
         <v>4.09</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0641</v>
+        <v>0.0631</v>
       </c>
       <c r="H222" t="n">
-        <v>0.0704</v>
+        <v>0.0696</v>
       </c>
       <c r="I222" t="n">
         <v>88</v>
@@ -8464,10 +8464,10 @@
         <v>4.09</v>
       </c>
       <c r="G223" t="n">
-        <v>0.0621</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>0.0683</v>
+        <v>0.0692</v>
       </c>
       <c r="I223" t="n">
         <v>89</v>
@@ -8500,10 +8500,10 @@
         <v>2.79</v>
       </c>
       <c r="G224" t="n">
-        <v>0.0539</v>
+        <v>0.053</v>
       </c>
       <c r="H224" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="I224" t="n">
         <v>90</v>
@@ -8536,10 +8536,10 @@
         <v>2.79</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0531</v>
+        <v>0.0529</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0856</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I225" t="n">
         <v>90</v>
@@ -8572,10 +8572,10 @@
         <v>2.79</v>
       </c>
       <c r="G226" t="n">
-        <v>0.0537</v>
+        <v>0.053</v>
       </c>
       <c r="H226" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="I226" t="n">
         <v>92</v>
@@ -8608,10 +8608,10 @@
         <v>6.29</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0732</v>
+        <v>0.0766</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0525</v>
+        <v>0.055</v>
       </c>
       <c r="I227" t="n">
         <v>88</v>
@@ -8680,10 +8680,10 @@
         <v>6.29</v>
       </c>
       <c r="G229" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0772</v>
       </c>
       <c r="H229" t="n">
-        <v>0.0547</v>
+        <v>0.0554</v>
       </c>
       <c r="I229" t="n">
         <v>92</v>
@@ -8716,10 +8716,10 @@
         <v>6.49</v>
       </c>
       <c r="G230" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="H230" t="n">
-        <v>0.05</v>
+        <v>0.0484</v>
       </c>
       <c r="I230" t="n">
         <v>88</v>
@@ -8752,10 +8752,10 @@
         <v>6.49</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0712</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0495</v>
+        <v>0.0483</v>
       </c>
       <c r="I231" t="n">
         <v>90</v>
@@ -8788,10 +8788,10 @@
         <v>6.49</v>
       </c>
       <c r="G232" t="n">
-        <v>0.0673</v>
+        <v>0.0688</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0468</v>
+        <v>0.0478</v>
       </c>
       <c r="I232" t="n">
         <v>89</v>
@@ -8824,10 +8824,10 @@
         <v>4.29</v>
       </c>
       <c r="G233" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0711</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0751</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I233" t="n">
         <v>91</v>
@@ -8860,10 +8860,10 @@
         <v>4.29</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0694</v>
+        <v>0.0708</v>
       </c>
       <c r="H234" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I234" t="n">
         <v>88</v>
@@ -8896,10 +8896,10 @@
         <v>4.29</v>
       </c>
       <c r="G235" t="n">
-        <v>0.0731</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H235" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0752</v>
       </c>
       <c r="I235" t="n">
         <v>92</v>
@@ -8932,10 +8932,10 @@
         <v>4.09</v>
       </c>
       <c r="G236" t="n">
-        <v>0.0635</v>
+        <v>0.063</v>
       </c>
       <c r="H236" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I236" t="n">
         <v>92</v>
@@ -8968,10 +8968,10 @@
         <v>4.09</v>
       </c>
       <c r="G237" t="n">
-        <v>0.0619</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0682</v>
+        <v>0.0692</v>
       </c>
       <c r="I237" t="n">
         <v>88</v>
@@ -9004,10 +9004,10 @@
         <v>4.09</v>
       </c>
       <c r="G238" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0633</v>
       </c>
       <c r="H238" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0699</v>
       </c>
       <c r="I238" t="n">
         <v>89</v>
@@ -9040,10 +9040,10 @@
         <v>2.79</v>
       </c>
       <c r="G239" t="n">
-        <v>0.0513</v>
+        <v>0.0525</v>
       </c>
       <c r="H239" t="n">
-        <v>0.083</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I239" t="n">
         <v>90</v>
@@ -9076,10 +9076,10 @@
         <v>2.79</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0532</v>
+        <v>0.0529</v>
       </c>
       <c r="H240" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0856</v>
       </c>
       <c r="I240" t="n">
         <v>91</v>
@@ -9112,10 +9112,10 @@
         <v>2.79</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0539</v>
+        <v>0.053</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0871</v>
+        <v>0.0858</v>
       </c>
       <c r="I241" t="n">
         <v>90</v>
